--- a/Versão5/ABNT/Ontologia_NBR15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2Q.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360AA962-F921-49CD-9A9F-2B31975D7D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B48DDF-1CE6-4758-9DC9-F2E91851A33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15379" uniqueCount="1517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15379" uniqueCount="1518">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4611,12 +4611,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -4632,16 +4626,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -5249,7 +5252,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FD276809-E4C5-4861-8007-253055573830}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="0"/>
@@ -5281,6 +5284,13 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -5631,14 +5641,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436D4E89-FEA8-43EC-BA63-D5F572124283}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5649,7 +5659,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>625</v>
       </c>
@@ -5660,7 +5670,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>626</v>
       </c>
@@ -5671,7 +5681,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5682,7 +5692,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5694,7 +5704,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5706,7 +5716,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5717,7 +5727,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
         <v>9</v>
       </c>
@@ -5728,7 +5738,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>627</v>
       </c>
@@ -5739,7 +5749,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>629</v>
       </c>
@@ -5750,7 +5760,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>630</v>
       </c>
@@ -5761,7 +5771,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5772,7 +5782,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>631</v>
       </c>
@@ -5783,7 +5793,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>632</v>
       </c>
@@ -5794,7 +5804,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>633</v>
       </c>
@@ -5805,7 +5815,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>634</v>
       </c>
@@ -5816,7 +5826,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5827,19 +5837,19 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>635</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46244.497396064813</v>
+        <v>46249.324131944442</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>1316</v>
       </c>
@@ -5850,7 +5860,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
         <v>1310</v>
       </c>
@@ -5862,7 +5872,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>1317</v>
       </c>
@@ -5874,7 +5884,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>624</v>
       </c>
@@ -5885,7 +5895,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>636</v>
       </c>
@@ -5896,7 +5906,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>641</v>
       </c>
@@ -5907,7 +5917,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>643</v>
       </c>
@@ -5918,7 +5928,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
         <v>1302</v>
       </c>
@@ -5929,7 +5939,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="38" t="s">
         <v>1477</v>
       </c>
@@ -5940,7 +5950,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="38" t="s">
         <v>1479</v>
       </c>
@@ -5951,7 +5961,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="s">
         <v>1481</v>
       </c>
@@ -5962,7 +5972,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38" t="s">
         <v>1483</v>
       </c>
@@ -5973,7 +5983,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="38" t="s">
         <v>1485</v>
       </c>
@@ -5984,7 +5994,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="38" t="s">
         <v>1487</v>
       </c>
@@ -5995,7 +6005,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="38" t="s">
         <v>1489</v>
       </c>
@@ -6006,7 +6016,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="38" t="s">
         <v>1491</v>
       </c>
@@ -6017,7 +6027,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="38" t="s">
         <v>1493</v>
       </c>
@@ -6028,7 +6038,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="38" t="s">
         <v>1495</v>
       </c>
@@ -6039,7 +6049,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="38" t="s">
         <v>1497</v>
       </c>
@@ -6050,7 +6060,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>1499</v>
       </c>
@@ -6061,7 +6071,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="73" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="73" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="38" t="s">
         <v>1501</v>
       </c>
@@ -6088,28 +6098,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA34"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.1640625" customWidth="1"/>
-    <col min="2" max="2" width="7" style="33" customWidth="1"/>
-    <col min="3" max="3" width="7.83203125" style="33" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" style="33" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.5" style="33"/>
-    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21" customWidth="1"/>
-    <col min="16" max="16" width="63.6640625" customWidth="1"/>
-    <col min="17" max="17" width="65.6640625" customWidth="1"/>
-    <col min="18" max="18" width="8.5" style="33"/>
-    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5" style="33"/>
-    <col min="24" max="24" width="46.6640625" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.09765625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.8984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35.8984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="56.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="37" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>1251</v>
       </c>
@@ -6192,7 +6208,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -6271,10 +6287,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="37" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="Y2" s="37" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="Z2" s="37" t="s">
         <v>1329</v>
@@ -6283,7 +6299,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -6362,10 +6378,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="37" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="Y3" s="37" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="Z3" s="37" t="s">
         <v>1330</v>
@@ -6374,7 +6390,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -6453,10 +6469,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y4" s="37" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="Z4" s="37" t="s">
         <v>1331</v>
@@ -6465,7 +6481,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -6544,10 +6560,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="37" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="Y5" s="37" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="Z5" s="37" t="s">
         <v>1332</v>
@@ -6556,7 +6572,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -6635,10 +6651,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y6" s="37" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="Z6" s="37" t="s">
         <v>1333</v>
@@ -6647,7 +6663,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -6726,10 +6742,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y7" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z7" s="37" t="s">
         <v>1334</v>
@@ -6738,7 +6754,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -6817,10 +6833,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y8" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z8" s="37" t="s">
         <v>1335</v>
@@ -6829,7 +6845,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -6908,10 +6924,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y9" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z9" s="37" t="s">
         <v>1243</v>
@@ -6920,7 +6936,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -6999,10 +7015,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y10" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z10" s="37" t="s">
         <v>1336</v>
@@ -7011,7 +7027,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -7090,10 +7106,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y11" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z11" s="37" t="s">
         <v>1337</v>
@@ -7102,7 +7118,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -7181,10 +7197,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="37" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="Y12" s="37" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="Z12" s="37" t="s">
         <v>1338</v>
@@ -7193,7 +7209,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -7272,10 +7288,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="37" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="Y13" s="37" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="Z13" s="37" t="s">
         <v>1339</v>
@@ -7284,7 +7300,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -7363,10 +7379,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="74" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="Y14" s="75" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="Z14" s="37" t="s">
         <v>1340</v>
@@ -7375,7 +7391,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -7455,10 +7471,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z15" s="63" t="s">
         <v>1362</v>
@@ -7468,7 +7484,7 @@
         <v>Design, Graphic, and IT Hardware Tools</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -7548,10 +7564,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y16" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z16" s="63" t="s">
         <v>1437</v>
@@ -7561,7 +7577,7 @@
         <v>IT Network Tools</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -7641,10 +7657,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y17" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z17" s="63" t="s">
         <v>1363</v>
@@ -7654,7 +7670,7 @@
         <v>Software tools for design, graphics or management</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -7734,10 +7750,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y18" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z18" s="63" t="s">
         <v>1364</v>
@@ -7747,7 +7763,7 @@
         <v>Measurement Tools</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -7827,10 +7843,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y19" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z19" s="63" t="s">
         <v>1365</v>
@@ -7840,7 +7856,7 @@
         <v>Monitoring Tools</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -7920,10 +7936,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y20" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z20" s="63" t="s">
         <v>1366</v>
@@ -7933,7 +7949,7 @@
         <v>Testing Tools</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -8013,10 +8029,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y21" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z21" s="63" t="s">
         <v>1367</v>
@@ -8026,7 +8042,7 @@
         <v>Construction Tools</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -8106,10 +8122,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y22" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z22" s="63" t="s">
         <v>1407</v>
@@ -8119,7 +8135,7 @@
         <v>Finishing Tools</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -8199,10 +8215,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y23" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z23" s="63" t="s">
         <v>1408</v>
@@ -8212,7 +8228,7 @@
         <v>Transportation Tools</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="55">
         <v>24</v>
       </c>
@@ -8292,10 +8308,10 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y24" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z24" s="63" t="s">
         <v>1409</v>
@@ -8305,7 +8321,7 @@
         <v>Power Tools</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="55">
         <v>25</v>
       </c>
@@ -8385,10 +8401,10 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y25" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z25" s="63" t="s">
         <v>1410</v>
@@ -8398,7 +8414,7 @@
         <v>Control Tools</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="55">
         <v>26</v>
       </c>
@@ -8478,10 +8494,10 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y26" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z26" s="63" t="s">
         <v>1411</v>
@@ -8491,7 +8507,7 @@
         <v>PPE Personal Protective Tools</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="55">
         <v>27</v>
       </c>
@@ -8571,10 +8587,10 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y27" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z27" s="63" t="s">
         <v>1412</v>
@@ -8584,7 +8600,7 @@
         <v>General Construction Tools</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="55">
         <v>28</v>
       </c>
@@ -8664,10 +8680,10 @@
         <v>Key-ABNT-28</v>
       </c>
       <c r="X28" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y28" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z28" s="63" t="s">
         <v>1413</v>
@@ -8677,7 +8693,7 @@
         <v>Construction Site Tools</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="55">
         <v>29</v>
       </c>
@@ -8757,10 +8773,10 @@
         <v>Key-ABNT-29</v>
       </c>
       <c r="X29" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y29" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z29" s="63" t="s">
         <v>1414</v>
@@ -8770,7 +8786,7 @@
         <v>Support Tools</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="55">
         <v>30</v>
       </c>
@@ -8850,10 +8866,10 @@
         <v>Key-ABNT-30</v>
       </c>
       <c r="X30" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y30" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z30" s="63" t="s">
         <v>1415</v>
@@ -8863,7 +8879,7 @@
         <v>Pumping and Tunneling Equipment</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="55">
         <v>31</v>
       </c>
@@ -8943,10 +8959,10 @@
         <v>Key-ABNT-31</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z31" s="63" t="s">
         <v>1368</v>
@@ -8956,7 +8972,7 @@
         <v>Concrete Production Equipment</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="55">
         <v>32</v>
       </c>
@@ -9036,10 +9052,10 @@
         <v>Key-ABNT-32</v>
       </c>
       <c r="X32" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y32" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z32" s="63" t="s">
         <v>1369</v>
@@ -9049,7 +9065,7 @@
         <v>Drilling &amp; Cutting Equipment</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="55">
         <v>33</v>
       </c>
@@ -9129,10 +9145,10 @@
         <v>Key-ABNT-33</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z33" s="63" t="s">
         <v>1370</v>
@@ -9142,7 +9158,7 @@
         <v>Equipment for Demolition and Earthmoving</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="55">
         <v>34</v>
       </c>
@@ -9222,10 +9238,10 @@
         <v>Key-ABNT-34</v>
       </c>
       <c r="X34" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Y34" s="37" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="Z34" s="63" t="s">
         <v>1371</v>
@@ -9237,10 +9253,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA34 A2:B34">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9255,13 +9276,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649E5DE9-BD63-4EDF-814C-ADC7DFAABB6E}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>1252</v>
       </c>
@@ -9326,7 +9347,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -9403,13 +9424,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBF1699-AA28-4D60-8669-5674605C36B3}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="3" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.69921875" customWidth="1"/>
+    <col min="2" max="3" width="14.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="17">
         <v>1</v>
       </c>
@@ -9420,7 +9441,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -9440,31 +9461,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y610"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.1640625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.19921875" style="20" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="20" customWidth="1"/>
     <col min="8" max="8" width="5" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.1640625" style="20" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="20" customWidth="1"/>
-    <col min="12" max="12" width="5.83203125" style="20" customWidth="1"/>
-    <col min="13" max="13" width="19.83203125" style="20" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.19921875" style="20" customWidth="1"/>
+    <col min="11" max="11" width="9.69921875" style="20" customWidth="1"/>
+    <col min="12" max="12" width="5.796875" style="20" customWidth="1"/>
+    <col min="13" max="13" width="19.796875" style="20" customWidth="1"/>
     <col min="14" max="14" width="7" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="20" customWidth="1"/>
-    <col min="17" max="17" width="5.33203125" style="20" customWidth="1"/>
-    <col min="18" max="19" width="5.83203125" style="20" customWidth="1"/>
-    <col min="20" max="25" width="4.6640625" style="20" customWidth="1"/>
-    <col min="26" max="16384" width="11.33203125" style="2"/>
+    <col min="15" max="15" width="49.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.796875" style="20" customWidth="1"/>
+    <col min="17" max="17" width="5.296875" style="20" customWidth="1"/>
+    <col min="18" max="19" width="5.796875" style="20" customWidth="1"/>
+    <col min="20" max="25" width="4.69921875" style="20" customWidth="1"/>
+    <col min="26" max="16384" width="11.296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>637</v>
       </c>
@@ -9541,7 +9562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -9618,7 +9639,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -9695,7 +9716,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -9772,7 +9793,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -9849,7 +9870,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -9926,7 +9947,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -10003,7 +10024,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -10080,7 +10101,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -10157,7 +10178,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -10234,7 +10255,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -10311,7 +10332,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -10388,7 +10409,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -10465,7 +10486,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -10542,7 +10563,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -10619,7 +10640,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -10696,7 +10717,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -10773,7 +10794,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -10850,7 +10871,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -10927,7 +10948,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -11004,7 +11025,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -11081,7 +11102,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -11158,7 +11179,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -11235,7 +11256,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -11312,7 +11333,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -11389,7 +11410,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -11466,7 +11487,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -11543,7 +11564,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -11620,7 +11641,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -11697,7 +11718,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43">
         <v>30</v>
       </c>
@@ -11774,7 +11795,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="43">
         <v>31</v>
       </c>
@@ -11851,7 +11872,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="43">
         <v>32</v>
       </c>
@@ -11928,7 +11949,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="43">
         <v>33</v>
       </c>
@@ -12005,7 +12026,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="43">
         <v>34</v>
       </c>
@@ -12082,7 +12103,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="43">
         <v>35</v>
       </c>
@@ -12159,7 +12180,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="43">
         <v>36</v>
       </c>
@@ -12236,7 +12257,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="43">
         <v>37</v>
       </c>
@@ -12313,7 +12334,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="43">
         <v>38</v>
       </c>
@@ -12390,7 +12411,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="43">
         <v>39</v>
       </c>
@@ -12467,7 +12488,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="43">
         <v>40</v>
       </c>
@@ -12544,7 +12565,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="43">
         <v>41</v>
       </c>
@@ -12621,7 +12642,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="43">
         <v>42</v>
       </c>
@@ -12698,7 +12719,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="43">
         <v>43</v>
       </c>
@@ -12775,7 +12796,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="43">
         <v>44</v>
       </c>
@@ -12852,7 +12873,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="43">
         <v>45</v>
       </c>
@@ -12929,7 +12950,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="43">
         <v>46</v>
       </c>
@@ -13006,7 +13027,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="43">
         <v>47</v>
       </c>
@@ -13083,7 +13104,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="43">
         <v>48</v>
       </c>
@@ -13160,7 +13181,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="43">
         <v>49</v>
       </c>
@@ -13237,7 +13258,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="43">
         <v>50</v>
       </c>
@@ -13314,7 +13335,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="43">
         <v>51</v>
       </c>
@@ -13391,7 +13412,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="43">
         <v>52</v>
       </c>
@@ -13468,7 +13489,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="43">
         <v>53</v>
       </c>
@@ -13545,7 +13566,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="43">
         <v>54</v>
       </c>
@@ -13622,7 +13643,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="43">
         <v>55</v>
       </c>
@@ -13699,7 +13720,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="43">
         <v>56</v>
       </c>
@@ -13776,7 +13797,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43">
         <v>57</v>
       </c>
@@ -13853,7 +13874,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43">
         <v>58</v>
       </c>
@@ -13930,7 +13951,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="43">
         <v>59</v>
       </c>
@@ -14007,7 +14028,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="43">
         <v>60</v>
       </c>
@@ -14084,7 +14105,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="43">
         <v>61</v>
       </c>
@@ -14161,7 +14182,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="43">
         <v>62</v>
       </c>
@@ -14238,7 +14259,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="43">
         <v>63</v>
       </c>
@@ -14315,7 +14336,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="43">
         <v>64</v>
       </c>
@@ -14392,7 +14413,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="43">
         <v>65</v>
       </c>
@@ -14469,7 +14490,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="43">
         <v>66</v>
       </c>
@@ -14546,7 +14567,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="43">
         <v>67</v>
       </c>
@@ -14623,7 +14644,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="43">
         <v>68</v>
       </c>
@@ -14700,7 +14721,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="43">
         <v>69</v>
       </c>
@@ -14777,7 +14798,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="43">
         <v>70</v>
       </c>
@@ -14854,7 +14875,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="43">
         <v>71</v>
       </c>
@@ -14931,7 +14952,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="43">
         <v>72</v>
       </c>
@@ -15008,7 +15029,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="43">
         <v>73</v>
       </c>
@@ -15085,7 +15106,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="43">
         <v>74</v>
       </c>
@@ -15162,7 +15183,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="43">
         <v>75</v>
       </c>
@@ -15239,7 +15260,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="43">
         <v>76</v>
       </c>
@@ -15316,7 +15337,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="43">
         <v>77</v>
       </c>
@@ -15393,7 +15414,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="43">
         <v>78</v>
       </c>
@@ -15470,7 +15491,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="43">
         <v>79</v>
       </c>
@@ -15547,7 +15568,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="43">
         <v>80</v>
       </c>
@@ -15624,7 +15645,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="43">
         <v>81</v>
       </c>
@@ -15701,7 +15722,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="43">
         <v>82</v>
       </c>
@@ -15778,7 +15799,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="43">
         <v>83</v>
       </c>
@@ -15855,7 +15876,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="43">
         <v>84</v>
       </c>
@@ -15932,7 +15953,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="43">
         <v>85</v>
       </c>
@@ -16009,7 +16030,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="43">
         <v>86</v>
       </c>
@@ -16086,7 +16107,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="43">
         <v>87</v>
       </c>
@@ -16163,7 +16184,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="43">
         <v>88</v>
       </c>
@@ -16240,7 +16261,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="43">
         <v>89</v>
       </c>
@@ -16317,7 +16338,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="43">
         <v>90</v>
       </c>
@@ -16394,7 +16415,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="43">
         <v>91</v>
       </c>
@@ -16471,7 +16492,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="43">
         <v>92</v>
       </c>
@@ -16548,7 +16569,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="43">
         <v>93</v>
       </c>
@@ -16625,7 +16646,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="43">
         <v>94</v>
       </c>
@@ -16702,7 +16723,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="43">
         <v>95</v>
       </c>
@@ -16779,7 +16800,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="43">
         <v>96</v>
       </c>
@@ -16856,7 +16877,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="43">
         <v>97</v>
       </c>
@@ -16933,7 +16954,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="43">
         <v>98</v>
       </c>
@@ -17010,7 +17031,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="43">
         <v>99</v>
       </c>
@@ -17087,7 +17108,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="43">
         <v>100</v>
       </c>
@@ -17164,7 +17185,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="43">
         <v>101</v>
       </c>
@@ -17241,7 +17262,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="43">
         <v>102</v>
       </c>
@@ -17318,7 +17339,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="43">
         <v>103</v>
       </c>
@@ -17395,7 +17416,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="43">
         <v>104</v>
       </c>
@@ -17472,7 +17493,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="43">
         <v>105</v>
       </c>
@@ -17549,7 +17570,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="43">
         <v>106</v>
       </c>
@@ -17626,7 +17647,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="43">
         <v>107</v>
       </c>
@@ -17703,7 +17724,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="43">
         <v>108</v>
       </c>
@@ -17780,7 +17801,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="43">
         <v>109</v>
       </c>
@@ -17857,7 +17878,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="43">
         <v>110</v>
       </c>
@@ -17934,7 +17955,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="43">
         <v>111</v>
       </c>
@@ -18011,7 +18032,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="43">
         <v>112</v>
       </c>
@@ -18088,7 +18109,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="43">
         <v>113</v>
       </c>
@@ -18165,7 +18186,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="43">
         <v>114</v>
       </c>
@@ -18242,7 +18263,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="43">
         <v>115</v>
       </c>
@@ -18319,7 +18340,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="43">
         <v>116</v>
       </c>
@@ -18396,7 +18417,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="43">
         <v>117</v>
       </c>
@@ -18473,7 +18494,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="43">
         <v>118</v>
       </c>
@@ -18550,7 +18571,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="43">
         <v>119</v>
       </c>
@@ -18627,7 +18648,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="43">
         <v>120</v>
       </c>
@@ -18704,7 +18725,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="43">
         <v>121</v>
       </c>
@@ -18781,7 +18802,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="43">
         <v>122</v>
       </c>
@@ -18858,7 +18879,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="43">
         <v>123</v>
       </c>
@@ -18935,7 +18956,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="43">
         <v>124</v>
       </c>
@@ -19012,7 +19033,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="43">
         <v>125</v>
       </c>
@@ -19089,7 +19110,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="43">
         <v>126</v>
       </c>
@@ -19166,7 +19187,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="43">
         <v>127</v>
       </c>
@@ -19243,7 +19264,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="43">
         <v>128</v>
       </c>
@@ -19320,7 +19341,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="43">
         <v>129</v>
       </c>
@@ -19397,7 +19418,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="43">
         <v>130</v>
       </c>
@@ -19474,7 +19495,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="43">
         <v>131</v>
       </c>
@@ -19551,7 +19572,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="43">
         <v>132</v>
       </c>
@@ -19628,7 +19649,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="43">
         <v>133</v>
       </c>
@@ -19705,7 +19726,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="43">
         <v>134</v>
       </c>
@@ -19782,7 +19803,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="43">
         <v>135</v>
       </c>
@@ -19859,7 +19880,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="43">
         <v>136</v>
       </c>
@@ -19936,7 +19957,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="43">
         <v>137</v>
       </c>
@@ -20013,7 +20034,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="43">
         <v>138</v>
       </c>
@@ -20090,7 +20111,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="43">
         <v>139</v>
       </c>
@@ -20167,7 +20188,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="43">
         <v>140</v>
       </c>
@@ -20244,7 +20265,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="43">
         <v>141</v>
       </c>
@@ -20321,7 +20342,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="43">
         <v>142</v>
       </c>
@@ -20398,7 +20419,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="43">
         <v>143</v>
       </c>
@@ -20475,7 +20496,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="43">
         <v>144</v>
       </c>
@@ -20552,7 +20573,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="43">
         <v>145</v>
       </c>
@@ -20629,7 +20650,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="43">
         <v>146</v>
       </c>
@@ -20706,7 +20727,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="43">
         <v>147</v>
       </c>
@@ -20783,7 +20804,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43">
         <v>148</v>
       </c>
@@ -20860,7 +20881,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="43">
         <v>149</v>
       </c>
@@ -20937,7 +20958,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="43">
         <v>150</v>
       </c>
@@ -21014,7 +21035,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="43">
         <v>151</v>
       </c>
@@ -21091,7 +21112,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43">
         <v>152</v>
       </c>
@@ -21168,7 +21189,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43">
         <v>153</v>
       </c>
@@ -21245,7 +21266,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="43">
         <v>154</v>
       </c>
@@ -21322,7 +21343,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="43">
         <v>155</v>
       </c>
@@ -21399,7 +21420,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="43">
         <v>156</v>
       </c>
@@ -21476,7 +21497,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="43">
         <v>157</v>
       </c>
@@ -21553,7 +21574,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="43">
         <v>158</v>
       </c>
@@ -21630,7 +21651,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="43">
         <v>159</v>
       </c>
@@ -21707,7 +21728,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="43">
         <v>160</v>
       </c>
@@ -21784,7 +21805,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="43">
         <v>161</v>
       </c>
@@ -21861,7 +21882,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="43">
         <v>162</v>
       </c>
@@ -21938,7 +21959,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43">
         <v>163</v>
       </c>
@@ -22015,7 +22036,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="43">
         <v>164</v>
       </c>
@@ -22092,7 +22113,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="43">
         <v>165</v>
       </c>
@@ -22169,7 +22190,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="43">
         <v>166</v>
       </c>
@@ -22246,7 +22267,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="43">
         <v>167</v>
       </c>
@@ -22323,7 +22344,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43">
         <v>168</v>
       </c>
@@ -22400,7 +22421,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43">
         <v>169</v>
       </c>
@@ -22477,7 +22498,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="43">
         <v>170</v>
       </c>
@@ -22554,7 +22575,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="43">
         <v>171</v>
       </c>
@@ -22631,7 +22652,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="43">
         <v>172</v>
       </c>
@@ -22708,7 +22729,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="43">
         <v>173</v>
       </c>
@@ -22785,7 +22806,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="43">
         <v>174</v>
       </c>
@@ -22862,7 +22883,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="43">
         <v>175</v>
       </c>
@@ -22939,7 +22960,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="43">
         <v>176</v>
       </c>
@@ -23016,7 +23037,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="43">
         <v>177</v>
       </c>
@@ -23093,7 +23114,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="43">
         <v>178</v>
       </c>
@@ -23170,7 +23191,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="43">
         <v>179</v>
       </c>
@@ -23247,7 +23268,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="43">
         <v>180</v>
       </c>
@@ -23324,7 +23345,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="43">
         <v>181</v>
       </c>
@@ -23401,7 +23422,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="43">
         <v>182</v>
       </c>
@@ -23478,7 +23499,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="43">
         <v>183</v>
       </c>
@@ -23555,7 +23576,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="43">
         <v>184</v>
       </c>
@@ -23632,7 +23653,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="43">
         <v>185</v>
       </c>
@@ -23709,7 +23730,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="43">
         <v>186</v>
       </c>
@@ -23786,7 +23807,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="43">
         <v>187</v>
       </c>
@@ -23863,7 +23884,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="43">
         <v>188</v>
       </c>
@@ -23940,7 +23961,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="43">
         <v>189</v>
       </c>
@@ -24017,7 +24038,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="43">
         <v>190</v>
       </c>
@@ -24094,7 +24115,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="43">
         <v>191</v>
       </c>
@@ -24171,7 +24192,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="43">
         <v>192</v>
       </c>
@@ -24248,7 +24269,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="43">
         <v>193</v>
       </c>
@@ -24325,7 +24346,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="43">
         <v>194</v>
       </c>
@@ -24402,7 +24423,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="43">
         <v>195</v>
       </c>
@@ -24479,7 +24500,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="43">
         <v>196</v>
       </c>
@@ -24556,7 +24577,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="43">
         <v>197</v>
       </c>
@@ -24633,7 +24654,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="43">
         <v>198</v>
       </c>
@@ -24710,7 +24731,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="43">
         <v>199</v>
       </c>
@@ -24787,7 +24808,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="43">
         <v>200</v>
       </c>
@@ -24864,7 +24885,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="43">
         <v>201</v>
       </c>
@@ -24941,7 +24962,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="43">
         <v>202</v>
       </c>
@@ -25018,7 +25039,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="43">
         <v>203</v>
       </c>
@@ -25095,7 +25116,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="43">
         <v>204</v>
       </c>
@@ -25172,7 +25193,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="43">
         <v>205</v>
       </c>
@@ -25249,7 +25270,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="43">
         <v>206</v>
       </c>
@@ -25326,7 +25347,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="43">
         <v>207</v>
       </c>
@@ -25403,7 +25424,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="43">
         <v>208</v>
       </c>
@@ -25480,7 +25501,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="43">
         <v>209</v>
       </c>
@@ -25557,7 +25578,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="43">
         <v>210</v>
       </c>
@@ -25634,7 +25655,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="43">
         <v>211</v>
       </c>
@@ -25711,7 +25732,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="43">
         <v>212</v>
       </c>
@@ -25788,7 +25809,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="43">
         <v>213</v>
       </c>
@@ -25865,7 +25886,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="43">
         <v>214</v>
       </c>
@@ -25942,7 +25963,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="43">
         <v>215</v>
       </c>
@@ -26019,7 +26040,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="43">
         <v>216</v>
       </c>
@@ -26096,7 +26117,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="43">
         <v>217</v>
       </c>
@@ -26173,7 +26194,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="43">
         <v>218</v>
       </c>
@@ -26250,7 +26271,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="43">
         <v>219</v>
       </c>
@@ -26327,7 +26348,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="43">
         <v>220</v>
       </c>
@@ -26404,7 +26425,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="43">
         <v>221</v>
       </c>
@@ -26481,7 +26502,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="43">
         <v>222</v>
       </c>
@@ -26558,7 +26579,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="43">
         <v>223</v>
       </c>
@@ -26635,7 +26656,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="43">
         <v>224</v>
       </c>
@@ -26712,7 +26733,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="43">
         <v>225</v>
       </c>
@@ -26789,7 +26810,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="43">
         <v>226</v>
       </c>
@@ -26866,7 +26887,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="43">
         <v>227</v>
       </c>
@@ -26943,7 +26964,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="43">
         <v>228</v>
       </c>
@@ -27020,7 +27041,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="43">
         <v>229</v>
       </c>
@@ -27097,7 +27118,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="43">
         <v>230</v>
       </c>
@@ -27174,7 +27195,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="43">
         <v>231</v>
       </c>
@@ -27251,7 +27272,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="43">
         <v>232</v>
       </c>
@@ -27328,7 +27349,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="43">
         <v>233</v>
       </c>
@@ -27405,7 +27426,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="43">
         <v>234</v>
       </c>
@@ -27482,7 +27503,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="43">
         <v>235</v>
       </c>
@@ -27559,7 +27580,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="43">
         <v>236</v>
       </c>
@@ -27636,7 +27657,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="43">
         <v>237</v>
       </c>
@@ -27713,7 +27734,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="43">
         <v>238</v>
       </c>
@@ -27790,7 +27811,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="43">
         <v>239</v>
       </c>
@@ -27867,7 +27888,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="43">
         <v>240</v>
       </c>
@@ -27944,7 +27965,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="43">
         <v>241</v>
       </c>
@@ -28021,7 +28042,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="43">
         <v>242</v>
       </c>
@@ -28098,7 +28119,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="43">
         <v>243</v>
       </c>
@@ -28175,7 +28196,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="43">
         <v>244</v>
       </c>
@@ -28252,7 +28273,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="43">
         <v>245</v>
       </c>
@@ -28329,7 +28350,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="43">
         <v>246</v>
       </c>
@@ -28406,7 +28427,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="43">
         <v>247</v>
       </c>
@@ -28483,7 +28504,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="43">
         <v>248</v>
       </c>
@@ -28560,7 +28581,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="43">
         <v>249</v>
       </c>
@@ -28637,7 +28658,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="43">
         <v>250</v>
       </c>
@@ -28714,7 +28735,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="43">
         <v>251</v>
       </c>
@@ -28791,7 +28812,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="43">
         <v>252</v>
       </c>
@@ -28868,7 +28889,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="43">
         <v>253</v>
       </c>
@@ -28945,7 +28966,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="43">
         <v>254</v>
       </c>
@@ -29022,7 +29043,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="43">
         <v>255</v>
       </c>
@@ -29099,7 +29120,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="43">
         <v>256</v>
       </c>
@@ -29176,7 +29197,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="43">
         <v>257</v>
       </c>
@@ -29253,7 +29274,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="43">
         <v>258</v>
       </c>
@@ -29330,7 +29351,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="43">
         <v>259</v>
       </c>
@@ -29407,7 +29428,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="43">
         <v>260</v>
       </c>
@@ -29484,7 +29505,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="43">
         <v>261</v>
       </c>
@@ -29561,7 +29582,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="43">
         <v>262</v>
       </c>
@@ -29638,7 +29659,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="43">
         <v>263</v>
       </c>
@@ -29715,7 +29736,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="43">
         <v>264</v>
       </c>
@@ -29792,7 +29813,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="43">
         <v>265</v>
       </c>
@@ -29869,7 +29890,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="43">
         <v>266</v>
       </c>
@@ -29946,7 +29967,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="43">
         <v>267</v>
       </c>
@@ -30023,7 +30044,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="43">
         <v>268</v>
       </c>
@@ -30100,7 +30121,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="43">
         <v>269</v>
       </c>
@@ -30177,7 +30198,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="43">
         <v>270</v>
       </c>
@@ -30254,7 +30275,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="43">
         <v>271</v>
       </c>
@@ -30331,7 +30352,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="43">
         <v>272</v>
       </c>
@@ -30408,7 +30429,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="43">
         <v>273</v>
       </c>
@@ -30485,7 +30506,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="43">
         <v>274</v>
       </c>
@@ -30562,7 +30583,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="43">
         <v>275</v>
       </c>
@@ -30639,7 +30660,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="43">
         <v>276</v>
       </c>
@@ -30716,7 +30737,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="43">
         <v>277</v>
       </c>
@@ -30793,7 +30814,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="43">
         <v>278</v>
       </c>
@@ -30870,7 +30891,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="43">
         <v>279</v>
       </c>
@@ -30947,7 +30968,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="43">
         <v>280</v>
       </c>
@@ -31024,7 +31045,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="43">
         <v>281</v>
       </c>
@@ -31101,7 +31122,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="43">
         <v>282</v>
       </c>
@@ -31178,7 +31199,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="43">
         <v>283</v>
       </c>
@@ -31255,7 +31276,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="43">
         <v>284</v>
       </c>
@@ -31332,7 +31353,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="43">
         <v>285</v>
       </c>
@@ -31409,7 +31430,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="43">
         <v>286</v>
       </c>
@@ -31486,7 +31507,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="43">
         <v>287</v>
       </c>
@@ -31563,7 +31584,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="43">
         <v>288</v>
       </c>
@@ -31640,7 +31661,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="43">
         <v>289</v>
       </c>
@@ -31717,7 +31738,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="43">
         <v>290</v>
       </c>
@@ -31794,7 +31815,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="43">
         <v>291</v>
       </c>
@@ -31871,7 +31892,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="43">
         <v>292</v>
       </c>
@@ -31948,7 +31969,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="43">
         <v>293</v>
       </c>
@@ -32025,7 +32046,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="43">
         <v>294</v>
       </c>
@@ -32102,7 +32123,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="43">
         <v>295</v>
       </c>
@@ -32179,7 +32200,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="43">
         <v>296</v>
       </c>
@@ -32256,7 +32277,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="43">
         <v>297</v>
       </c>
@@ -32333,7 +32354,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="43">
         <v>298</v>
       </c>
@@ -32410,7 +32431,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="43">
         <v>299</v>
       </c>
@@ -32487,7 +32508,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="43">
         <v>300</v>
       </c>
@@ -32564,7 +32585,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="43">
         <v>301</v>
       </c>
@@ -32641,7 +32662,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="43">
         <v>302</v>
       </c>
@@ -32718,7 +32739,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="43">
         <v>303</v>
       </c>
@@ -32795,7 +32816,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="43">
         <v>304</v>
       </c>
@@ -32872,7 +32893,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="43">
         <v>305</v>
       </c>
@@ -32949,7 +32970,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="43">
         <v>306</v>
       </c>
@@ -33026,7 +33047,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="43">
         <v>307</v>
       </c>
@@ -33103,7 +33124,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="43">
         <v>308</v>
       </c>
@@ -33180,7 +33201,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="43">
         <v>309</v>
       </c>
@@ -33257,7 +33278,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="43">
         <v>310</v>
       </c>
@@ -33334,7 +33355,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="43">
         <v>311</v>
       </c>
@@ -33411,7 +33432,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="43">
         <v>312</v>
       </c>
@@ -33488,7 +33509,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="43">
         <v>313</v>
       </c>
@@ -33565,7 +33586,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="43">
         <v>314</v>
       </c>
@@ -33642,7 +33663,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="43">
         <v>315</v>
       </c>
@@ -33719,7 +33740,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="43">
         <v>316</v>
       </c>
@@ -33796,7 +33817,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="43">
         <v>317</v>
       </c>
@@ -33873,7 +33894,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="43">
         <v>318</v>
       </c>
@@ -33950,7 +33971,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="43">
         <v>319</v>
       </c>
@@ -34027,7 +34048,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="43">
         <v>320</v>
       </c>
@@ -34104,7 +34125,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="43">
         <v>321</v>
       </c>
@@ -34181,7 +34202,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="43">
         <v>322</v>
       </c>
@@ -34258,7 +34279,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="43">
         <v>323</v>
       </c>
@@ -34335,7 +34356,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="43">
         <v>324</v>
       </c>
@@ -34412,7 +34433,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="43">
         <v>325</v>
       </c>
@@ -34489,7 +34510,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="43">
         <v>326</v>
       </c>
@@ -34566,7 +34587,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="43">
         <v>327</v>
       </c>
@@ -34643,7 +34664,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="43">
         <v>328</v>
       </c>
@@ -34720,7 +34741,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="43">
         <v>329</v>
       </c>
@@ -34797,7 +34818,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="43">
         <v>330</v>
       </c>
@@ -34874,7 +34895,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="43">
         <v>331</v>
       </c>
@@ -34951,7 +34972,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="43">
         <v>332</v>
       </c>
@@ -35028,7 +35049,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="43">
         <v>333</v>
       </c>
@@ -35105,7 +35126,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="43">
         <v>334</v>
       </c>
@@ -35182,7 +35203,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="43">
         <v>335</v>
       </c>
@@ -35259,7 +35280,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="43">
         <v>336</v>
       </c>
@@ -35336,7 +35357,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="43">
         <v>337</v>
       </c>
@@ -35413,7 +35434,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="43">
         <v>338</v>
       </c>
@@ -35490,7 +35511,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="43">
         <v>339</v>
       </c>
@@ -35567,7 +35588,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="43">
         <v>340</v>
       </c>
@@ -35644,7 +35665,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="43">
         <v>341</v>
       </c>
@@ -35721,7 +35742,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="43">
         <v>342</v>
       </c>
@@ -35798,7 +35819,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="43">
         <v>343</v>
       </c>
@@ -35875,7 +35896,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="43">
         <v>344</v>
       </c>
@@ -35952,7 +35973,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="43">
         <v>345</v>
       </c>
@@ -36029,7 +36050,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="43">
         <v>346</v>
       </c>
@@ -36106,7 +36127,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="43">
         <v>347</v>
       </c>
@@ -36183,7 +36204,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="43">
         <v>348</v>
       </c>
@@ -36260,7 +36281,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="43">
         <v>349</v>
       </c>
@@ -36337,7 +36358,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="43">
         <v>350</v>
       </c>
@@ -36414,7 +36435,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="43">
         <v>351</v>
       </c>
@@ -36491,7 +36512,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="43">
         <v>352</v>
       </c>
@@ -36568,7 +36589,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="43">
         <v>353</v>
       </c>
@@ -36645,7 +36666,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="43">
         <v>354</v>
       </c>
@@ -36722,7 +36743,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="43">
         <v>355</v>
       </c>
@@ -36799,7 +36820,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="43">
         <v>356</v>
       </c>
@@ -36876,7 +36897,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="43">
         <v>357</v>
       </c>
@@ -36953,7 +36974,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="43">
         <v>358</v>
       </c>
@@ -37030,7 +37051,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="43">
         <v>359</v>
       </c>
@@ -37107,7 +37128,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="43">
         <v>360</v>
       </c>
@@ -37184,7 +37205,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="43">
         <v>361</v>
       </c>
@@ -37261,7 +37282,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="43">
         <v>362</v>
       </c>
@@ -37338,7 +37359,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="43">
         <v>363</v>
       </c>
@@ -37415,7 +37436,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="43">
         <v>364</v>
       </c>
@@ -37492,7 +37513,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="43">
         <v>365</v>
       </c>
@@ -37569,7 +37590,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="43">
         <v>366</v>
       </c>
@@ -37646,7 +37667,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="43">
         <v>367</v>
       </c>
@@ -37723,7 +37744,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="43">
         <v>368</v>
       </c>
@@ -37800,7 +37821,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="43">
         <v>369</v>
       </c>
@@ -37877,7 +37898,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="43">
         <v>370</v>
       </c>
@@ -37954,7 +37975,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="43">
         <v>371</v>
       </c>
@@ -38031,7 +38052,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="43">
         <v>372</v>
       </c>
@@ -38108,7 +38129,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="43">
         <v>373</v>
       </c>
@@ -38185,7 +38206,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="43">
         <v>374</v>
       </c>
@@ -38262,7 +38283,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="375" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="43">
         <v>375</v>
       </c>
@@ -38339,7 +38360,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="376" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="43">
         <v>376</v>
       </c>
@@ -38416,7 +38437,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="377" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="43">
         <v>377</v>
       </c>
@@ -38493,7 +38514,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="378" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="43">
         <v>378</v>
       </c>
@@ -38570,7 +38591,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="379" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="43">
         <v>379</v>
       </c>
@@ -38647,7 +38668,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="380" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="43">
         <v>380</v>
       </c>
@@ -38724,7 +38745,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="381" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="43">
         <v>381</v>
       </c>
@@ -38801,7 +38822,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="382" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="43">
         <v>382</v>
       </c>
@@ -38878,7 +38899,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="383" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="43">
         <v>383</v>
       </c>
@@ -38955,7 +38976,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="384" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="43">
         <v>384</v>
       </c>
@@ -39032,7 +39053,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="385" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="43">
         <v>385</v>
       </c>
@@ -39109,7 +39130,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="386" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="43">
         <v>386</v>
       </c>
@@ -39186,7 +39207,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="387" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="43">
         <v>387</v>
       </c>
@@ -39263,7 +39284,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="388" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="43">
         <v>388</v>
       </c>
@@ -39340,7 +39361,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="389" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="43">
         <v>389</v>
       </c>
@@ -39417,7 +39438,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="390" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="43">
         <v>390</v>
       </c>
@@ -39494,7 +39515,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="391" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="43">
         <v>391</v>
       </c>
@@ -39571,7 +39592,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="392" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="43">
         <v>392</v>
       </c>
@@ -39648,7 +39669,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="393" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="43">
         <v>393</v>
       </c>
@@ -39725,7 +39746,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="394" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="43">
         <v>394</v>
       </c>
@@ -39802,7 +39823,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="395" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="43">
         <v>395</v>
       </c>
@@ -39879,7 +39900,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="396" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="43">
         <v>396</v>
       </c>
@@ -39956,7 +39977,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="397" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="43">
         <v>397</v>
       </c>
@@ -40033,7 +40054,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="398" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="43">
         <v>398</v>
       </c>
@@ -40110,7 +40131,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="399" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="43">
         <v>399</v>
       </c>
@@ -40187,7 +40208,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="400" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="43">
         <v>400</v>
       </c>
@@ -40264,7 +40285,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="401" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="43">
         <v>401</v>
       </c>
@@ -40341,7 +40362,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="402" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="43">
         <v>402</v>
       </c>
@@ -40418,7 +40439,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="403" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="43">
         <v>403</v>
       </c>
@@ -40495,7 +40516,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="404" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="43">
         <v>404</v>
       </c>
@@ -40572,7 +40593,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="405" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="43">
         <v>405</v>
       </c>
@@ -40649,7 +40670,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="406" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="43">
         <v>406</v>
       </c>
@@ -40726,7 +40747,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="407" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="43">
         <v>407</v>
       </c>
@@ -40803,7 +40824,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="408" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="43">
         <v>408</v>
       </c>
@@ -40880,7 +40901,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="409" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="43">
         <v>409</v>
       </c>
@@ -40957,7 +40978,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="410" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="43">
         <v>410</v>
       </c>
@@ -41034,7 +41055,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="411" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="43">
         <v>411</v>
       </c>
@@ -41111,7 +41132,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="412" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="43">
         <v>412</v>
       </c>
@@ -41188,7 +41209,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="413" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="43">
         <v>413</v>
       </c>
@@ -41265,7 +41286,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="414" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="43">
         <v>414</v>
       </c>
@@ -41342,7 +41363,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="415" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="43">
         <v>415</v>
       </c>
@@ -41419,7 +41440,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="416" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="43">
         <v>416</v>
       </c>
@@ -41496,7 +41517,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="417" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="43">
         <v>417</v>
       </c>
@@ -41573,7 +41594,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="418" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="43">
         <v>418</v>
       </c>
@@ -41650,7 +41671,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="419" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="43">
         <v>419</v>
       </c>
@@ -41727,7 +41748,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="420" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="43">
         <v>420</v>
       </c>
@@ -41804,7 +41825,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="421" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="43">
         <v>421</v>
       </c>
@@ -41881,7 +41902,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="422" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="43">
         <v>422</v>
       </c>
@@ -41958,7 +41979,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="423" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="43">
         <v>423</v>
       </c>
@@ -42035,7 +42056,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="424" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="43">
         <v>424</v>
       </c>
@@ -42112,7 +42133,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="425" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="43">
         <v>425</v>
       </c>
@@ -42189,7 +42210,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="426" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="43">
         <v>426</v>
       </c>
@@ -42266,7 +42287,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="427" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="43">
         <v>427</v>
       </c>
@@ -42343,7 +42364,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="428" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="43">
         <v>428</v>
       </c>
@@ -42420,7 +42441,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="429" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="43">
         <v>429</v>
       </c>
@@ -42497,7 +42518,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="430" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="43">
         <v>430</v>
       </c>
@@ -42574,7 +42595,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="431" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="43">
         <v>431</v>
       </c>
@@ -42651,7 +42672,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="432" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="43">
         <v>432</v>
       </c>
@@ -42728,7 +42749,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="433" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="43">
         <v>433</v>
       </c>
@@ -42805,7 +42826,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="434" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="43">
         <v>434</v>
       </c>
@@ -42882,7 +42903,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="435" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="43">
         <v>435</v>
       </c>
@@ -42959,7 +42980,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="436" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="43">
         <v>436</v>
       </c>
@@ -43036,7 +43057,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="437" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="43">
         <v>437</v>
       </c>
@@ -43113,7 +43134,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="438" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="43">
         <v>438</v>
       </c>
@@ -43190,7 +43211,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="439" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="43">
         <v>439</v>
       </c>
@@ -43267,7 +43288,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="440" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="43">
         <v>440</v>
       </c>
@@ -43344,7 +43365,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="441" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="43">
         <v>441</v>
       </c>
@@ -43421,7 +43442,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="442" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="43">
         <v>442</v>
       </c>
@@ -43498,7 +43519,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="443" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="43">
         <v>443</v>
       </c>
@@ -43575,7 +43596,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="444" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="43">
         <v>444</v>
       </c>
@@ -43652,7 +43673,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="445" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="43">
         <v>445</v>
       </c>
@@ -43729,7 +43750,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="446" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="43">
         <v>446</v>
       </c>
@@ -43806,7 +43827,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="447" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="43">
         <v>447</v>
       </c>
@@ -43883,7 +43904,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="448" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="43">
         <v>448</v>
       </c>
@@ -43960,7 +43981,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="449" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="43">
         <v>449</v>
       </c>
@@ -44037,7 +44058,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="450" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="43">
         <v>450</v>
       </c>
@@ -44114,7 +44135,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="451" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="43">
         <v>451</v>
       </c>
@@ -44191,7 +44212,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="452" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="43">
         <v>452</v>
       </c>
@@ -44268,7 +44289,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="453" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="43">
         <v>453</v>
       </c>
@@ -44345,7 +44366,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="454" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="43">
         <v>454</v>
       </c>
@@ -44422,7 +44443,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="455" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="43">
         <v>455</v>
       </c>
@@ -44499,7 +44520,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="456" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="43">
         <v>456</v>
       </c>
@@ -44576,7 +44597,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="457" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="43">
         <v>457</v>
       </c>
@@ -44653,7 +44674,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="458" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="43">
         <v>458</v>
       </c>
@@ -44730,7 +44751,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="459" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="43">
         <v>459</v>
       </c>
@@ -44807,7 +44828,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="460" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="43">
         <v>460</v>
       </c>
@@ -44884,7 +44905,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="461" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="43">
         <v>461</v>
       </c>
@@ -44961,7 +44982,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="462" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="43">
         <v>462</v>
       </c>
@@ -45038,7 +45059,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="463" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="43">
         <v>463</v>
       </c>
@@ -45115,7 +45136,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="464" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="43">
         <v>464</v>
       </c>
@@ -45192,7 +45213,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="465" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="43">
         <v>465</v>
       </c>
@@ -45269,7 +45290,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="466" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="43">
         <v>466</v>
       </c>
@@ -45346,7 +45367,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="467" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="43">
         <v>467</v>
       </c>
@@ -45423,7 +45444,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="468" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="43">
         <v>468</v>
       </c>
@@ -45500,7 +45521,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="469" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="43">
         <v>469</v>
       </c>
@@ -45577,7 +45598,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="470" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="43">
         <v>470</v>
       </c>
@@ -45654,7 +45675,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="471" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="43">
         <v>471</v>
       </c>
@@ -45731,7 +45752,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="472" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="43">
         <v>472</v>
       </c>
@@ -45808,7 +45829,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="473" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="43">
         <v>473</v>
       </c>
@@ -45885,7 +45906,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="474" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="43">
         <v>474</v>
       </c>
@@ -45962,7 +45983,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="475" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="43">
         <v>475</v>
       </c>
@@ -46039,7 +46060,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="476" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="43">
         <v>476</v>
       </c>
@@ -46116,7 +46137,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="477" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="43">
         <v>477</v>
       </c>
@@ -46193,7 +46214,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="478" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="43">
         <v>478</v>
       </c>
@@ -46270,7 +46291,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="479" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="43">
         <v>479</v>
       </c>
@@ -46347,7 +46368,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="480" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="43">
         <v>480</v>
       </c>
@@ -46424,7 +46445,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="481" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="43">
         <v>481</v>
       </c>
@@ -46501,7 +46522,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="482" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="43">
         <v>482</v>
       </c>
@@ -46578,7 +46599,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="483" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="43">
         <v>483</v>
       </c>
@@ -46655,7 +46676,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="484" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="43">
         <v>484</v>
       </c>
@@ -46732,7 +46753,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="485" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="43">
         <v>485</v>
       </c>
@@ -46809,7 +46830,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="486" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="43">
         <v>486</v>
       </c>
@@ -46886,7 +46907,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="487" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="43">
         <v>487</v>
       </c>
@@ -46963,7 +46984,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="488" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="43">
         <v>488</v>
       </c>
@@ -47040,7 +47061,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="489" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="43">
         <v>489</v>
       </c>
@@ -47117,7 +47138,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="490" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="43">
         <v>490</v>
       </c>
@@ -47194,7 +47215,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="491" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="43">
         <v>491</v>
       </c>
@@ -47271,7 +47292,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="492" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="43">
         <v>492</v>
       </c>
@@ -47348,7 +47369,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="493" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="43">
         <v>493</v>
       </c>
@@ -47425,7 +47446,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="494" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="43">
         <v>494</v>
       </c>
@@ -47502,7 +47523,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="495" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="43">
         <v>495</v>
       </c>
@@ -47579,7 +47600,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="496" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="43">
         <v>496</v>
       </c>
@@ -47656,7 +47677,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="497" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="43">
         <v>497</v>
       </c>
@@ -47733,7 +47754,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="498" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="43">
         <v>498</v>
       </c>
@@ -47810,7 +47831,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="499" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="43">
         <v>499</v>
       </c>
@@ -47887,7 +47908,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="43">
         <v>500</v>
       </c>
@@ -47964,7 +47985,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="501" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="43">
         <v>501</v>
       </c>
@@ -48041,7 +48062,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="502" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="43">
         <v>502</v>
       </c>
@@ -48118,7 +48139,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="503" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="43">
         <v>503</v>
       </c>
@@ -48195,7 +48216,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="504" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="43">
         <v>504</v>
       </c>
@@ -48272,7 +48293,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="505" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="43">
         <v>505</v>
       </c>
@@ -48349,7 +48370,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="506" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="43">
         <v>506</v>
       </c>
@@ -48426,7 +48447,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="507" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="43">
         <v>507</v>
       </c>
@@ -48503,7 +48524,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="508" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="43">
         <v>508</v>
       </c>
@@ -48580,7 +48601,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="509" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="43">
         <v>509</v>
       </c>
@@ -48657,7 +48678,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="510" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="43">
         <v>510</v>
       </c>
@@ -48734,7 +48755,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="511" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="43">
         <v>511</v>
       </c>
@@ -48811,7 +48832,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="512" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="43">
         <v>512</v>
       </c>
@@ -48888,7 +48909,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="513" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="43">
         <v>513</v>
       </c>
@@ -48965,7 +48986,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="514" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="43">
         <v>514</v>
       </c>
@@ -49042,7 +49063,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="515" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="43">
         <v>515</v>
       </c>
@@ -49119,7 +49140,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="516" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="43">
         <v>516</v>
       </c>
@@ -49196,7 +49217,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="517" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="43">
         <v>517</v>
       </c>
@@ -49273,7 +49294,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="518" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="43">
         <v>518</v>
       </c>
@@ -49350,7 +49371,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="519" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="43">
         <v>519</v>
       </c>
@@ -49427,7 +49448,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="520" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="43">
         <v>520</v>
       </c>
@@ -49504,7 +49525,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="521" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="43">
         <v>521</v>
       </c>
@@ -49581,7 +49602,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="522" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="43">
         <v>522</v>
       </c>
@@ -49658,7 +49679,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="523" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="43">
         <v>523</v>
       </c>
@@ -49735,7 +49756,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="524" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="43">
         <v>524</v>
       </c>
@@ -49812,7 +49833,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="525" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="43">
         <v>525</v>
       </c>
@@ -49889,7 +49910,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="526" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="43">
         <v>526</v>
       </c>
@@ -49966,7 +49987,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="527" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="43">
         <v>527</v>
       </c>
@@ -50043,7 +50064,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="528" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="43">
         <v>528</v>
       </c>
@@ -50120,7 +50141,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="529" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="43">
         <v>529</v>
       </c>
@@ -50197,7 +50218,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="530" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="43">
         <v>530</v>
       </c>
@@ -50274,7 +50295,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="531" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="43">
         <v>531</v>
       </c>
@@ -50351,7 +50372,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="532" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="43">
         <v>532</v>
       </c>
@@ -50428,7 +50449,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="533" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="43">
         <v>533</v>
       </c>
@@ -50505,7 +50526,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="534" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="43">
         <v>534</v>
       </c>
@@ -50582,7 +50603,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="535" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="43">
         <v>535</v>
       </c>
@@ -50659,7 +50680,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="536" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="43">
         <v>536</v>
       </c>
@@ -50736,7 +50757,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="537" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="43">
         <v>537</v>
       </c>
@@ -50813,7 +50834,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="538" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="43">
         <v>538</v>
       </c>
@@ -50890,7 +50911,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="539" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="43">
         <v>539</v>
       </c>
@@ -50967,7 +50988,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="540" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="43">
         <v>540</v>
       </c>
@@ -51044,7 +51065,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="541" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="43">
         <v>541</v>
       </c>
@@ -51121,7 +51142,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="542" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="43">
         <v>542</v>
       </c>
@@ -51198,7 +51219,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="543" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="43">
         <v>543</v>
       </c>
@@ -51275,7 +51296,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="544" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="43">
         <v>544</v>
       </c>
@@ -51352,7 +51373,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="545" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="43">
         <v>545</v>
       </c>
@@ -51429,7 +51450,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="546" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="43">
         <v>546</v>
       </c>
@@ -51506,7 +51527,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="547" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="43">
         <v>547</v>
       </c>
@@ -51583,7 +51604,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="548" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="43">
         <v>548</v>
       </c>
@@ -51660,7 +51681,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="549" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="43">
         <v>549</v>
       </c>
@@ -51737,7 +51758,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="550" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="43">
         <v>550</v>
       </c>
@@ -51814,7 +51835,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="551" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="43">
         <v>551</v>
       </c>
@@ -51891,7 +51912,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="552" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="43">
         <v>552</v>
       </c>
@@ -51968,7 +51989,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="553" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="43">
         <v>553</v>
       </c>
@@ -52045,7 +52066,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="554" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="43">
         <v>554</v>
       </c>
@@ -52122,7 +52143,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="555" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="43">
         <v>555</v>
       </c>
@@ -52199,7 +52220,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="556" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="43">
         <v>556</v>
       </c>
@@ -52276,7 +52297,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="557" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="43">
         <v>557</v>
       </c>
@@ -52353,7 +52374,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="558" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="43">
         <v>558</v>
       </c>
@@ -52430,7 +52451,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="559" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="43">
         <v>559</v>
       </c>
@@ -52507,7 +52528,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="560" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="43">
         <v>560</v>
       </c>
@@ -52584,7 +52605,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="561" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="43">
         <v>561</v>
       </c>
@@ -52661,7 +52682,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="562" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="43">
         <v>562</v>
       </c>
@@ -52738,7 +52759,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="563" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="43">
         <v>563</v>
       </c>
@@ -52815,7 +52836,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="564" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="43">
         <v>564</v>
       </c>
@@ -52892,7 +52913,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="565" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="43">
         <v>565</v>
       </c>
@@ -52969,7 +52990,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="566" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="43">
         <v>566</v>
       </c>
@@ -53046,7 +53067,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="567" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="43">
         <v>567</v>
       </c>
@@ -53123,7 +53144,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="568" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="43">
         <v>568</v>
       </c>
@@ -53200,7 +53221,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="569" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="43">
         <v>569</v>
       </c>
@@ -53277,7 +53298,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="570" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="43">
         <v>570</v>
       </c>
@@ -53354,7 +53375,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="571" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="43">
         <v>571</v>
       </c>
@@ -53431,7 +53452,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="572" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="43">
         <v>572</v>
       </c>
@@ -53508,7 +53529,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="573" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="43">
         <v>573</v>
       </c>
@@ -53585,7 +53606,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="574" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="43">
         <v>574</v>
       </c>
@@ -53662,7 +53683,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="575" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="43">
         <v>575</v>
       </c>
@@ -53739,7 +53760,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="576" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="43">
         <v>576</v>
       </c>
@@ -53816,7 +53837,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="577" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="43">
         <v>577</v>
       </c>
@@ -53893,7 +53914,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="578" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="43">
         <v>578</v>
       </c>
@@ -53970,7 +53991,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="579" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="43">
         <v>579</v>
       </c>
@@ -54047,7 +54068,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="580" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="43">
         <v>580</v>
       </c>
@@ -54124,7 +54145,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="581" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="43">
         <v>581</v>
       </c>
@@ -54201,7 +54222,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="582" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="43">
         <v>582</v>
       </c>
@@ -54278,7 +54299,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="583" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="43">
         <v>583</v>
       </c>
@@ -54355,7 +54376,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="584" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="43">
         <v>584</v>
       </c>
@@ -54432,7 +54453,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="585" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="43">
         <v>585</v>
       </c>
@@ -54509,7 +54530,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="586" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="43">
         <v>586</v>
       </c>
@@ -54586,7 +54607,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="587" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="43">
         <v>587</v>
       </c>
@@ -54663,7 +54684,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="588" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="43">
         <v>588</v>
       </c>
@@ -54740,7 +54761,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="589" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="43">
         <v>589</v>
       </c>
@@ -54817,7 +54838,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="590" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="43">
         <v>590</v>
       </c>
@@ -54894,7 +54915,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="591" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="43">
         <v>591</v>
       </c>
@@ -54971,7 +54992,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="592" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="43">
         <v>592</v>
       </c>
@@ -55048,7 +55069,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="593" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="43">
         <v>593</v>
       </c>
@@ -55125,7 +55146,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="594" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="43">
         <v>594</v>
       </c>
@@ -55202,7 +55223,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="595" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="43">
         <v>595</v>
       </c>
@@ -55279,7 +55300,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="596" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="43">
         <v>596</v>
       </c>
@@ -55356,7 +55377,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="597" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="43">
         <v>597</v>
       </c>
@@ -55433,7 +55454,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="598" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="43">
         <v>598</v>
       </c>
@@ -55510,7 +55531,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="599" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="43">
         <v>599</v>
       </c>
@@ -55587,7 +55608,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="600" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="43">
         <v>600</v>
       </c>
@@ -55664,7 +55685,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="601" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="43">
         <v>601</v>
       </c>
@@ -55741,7 +55762,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="602" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="43">
         <v>602</v>
       </c>
@@ -55818,7 +55839,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="603" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="43">
         <v>603</v>
       </c>
@@ -55895,7 +55916,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="604" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="43">
         <v>604</v>
       </c>
@@ -55972,7 +55993,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="605" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="43">
         <v>605</v>
       </c>
@@ -56049,7 +56070,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="606" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="43">
         <v>606</v>
       </c>
@@ -56126,7 +56147,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="607" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="43">
         <v>607</v>
       </c>
@@ -56203,7 +56224,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="608" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="43">
         <v>608</v>
       </c>
@@ -56280,7 +56301,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="609" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="43">
         <v>609</v>
       </c>
@@ -56357,7 +56378,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="610" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="43">
         <v>610</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2Q.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B48DDF-1CE6-4758-9DC9-F2E91851A33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A008867B-646C-4B7A-90AF-6A0E1FC22587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15379" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15487" uniqueCount="1560">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4645,6 +4645,132 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
+  </si>
+  <si>
+    <t>Herramientas de software para diseño, gráficos o gestión</t>
+  </si>
+  <si>
+    <t>Herramientas de medición</t>
+  </si>
+  <si>
+    <t>Herramientas eléctricas</t>
+  </si>
+  <si>
+    <t>Herramientas de control</t>
+  </si>
+  <si>
+    <t>Equipos para demolición y movimiento de tierras</t>
+  </si>
+  <si>
+    <t>Equipos para limpieza de fachadas</t>
+  </si>
+  <si>
+    <t>Equipment for cutting and drill</t>
+  </si>
+  <si>
+    <t>Design, Graphic, and IT Hardware Tools</t>
+  </si>
+  <si>
+    <t>IT Network Tools</t>
+  </si>
+  <si>
+    <t>Software tools for design, graphics or management</t>
+  </si>
+  <si>
+    <t>Measurement Tools</t>
+  </si>
+  <si>
+    <t>Monitoring Tools</t>
+  </si>
+  <si>
+    <t>Testing Tools</t>
+  </si>
+  <si>
+    <t>Construction Tools</t>
+  </si>
+  <si>
+    <t>Finishing Tools</t>
+  </si>
+  <si>
+    <t>Transportation Tools</t>
+  </si>
+  <si>
+    <t>Power Tools</t>
+  </si>
+  <si>
+    <t>Control Tools</t>
+  </si>
+  <si>
+    <t>PPE Personal Protective Tools</t>
+  </si>
+  <si>
+    <t>General Construction Tools</t>
+  </si>
+  <si>
+    <t>Construction Site Tools</t>
+  </si>
+  <si>
+    <t>Support Tools</t>
+  </si>
+  <si>
+    <t>Pumping and Tunneling Equipment</t>
+  </si>
+  <si>
+    <t>Concrete Production Equipment</t>
+  </si>
+  <si>
+    <t>Equipment for Demolition and Earthmoving</t>
+  </si>
+  <si>
+    <t>Equipment for Cleaning and Maintenance of Facades</t>
+  </si>
+  <si>
+    <t>Herramientas de diseño, gráficos y hardware de TI</t>
+  </si>
+  <si>
+    <t>Herramientas de Red TI</t>
+  </si>
+  <si>
+    <t>Herramientas de monitorización</t>
+  </si>
+  <si>
+    <t>Herramientas de prueba</t>
+  </si>
+  <si>
+    <t>Herramientas de construcción</t>
+  </si>
+  <si>
+    <t>Herramientas de acabado</t>
+  </si>
+  <si>
+    <t>Herramientas de transporte</t>
+  </si>
+  <si>
+    <t>Herramientas de protección individual individual (EPP)</t>
+  </si>
+  <si>
+    <t>Herramientas generales de construcción</t>
+  </si>
+  <si>
+    <t>Herramientas para obras</t>
+  </si>
+  <si>
+    <t>Herramientas de soporte</t>
+  </si>
+  <si>
+    <t>Equipos de bombeo y túneles</t>
+  </si>
+  <si>
+    <t>Equipos de producción de hormigón</t>
+  </si>
+  <si>
+    <t>Equipos de perforación y corte</t>
   </si>
 </sst>
 </file>
@@ -5213,9 +5339,6 @@
     <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5246,13 +5369,16 @@
     <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FD276809-E4C5-4861-8007-253055573830}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
     <dxf>
       <font>
         <b val="0"/>
@@ -5278,6 +5404,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -5641,14 +5775,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436D4E89-FEA8-43EC-BA63-D5F572124283}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5659,7 +5793,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>625</v>
       </c>
@@ -5670,7 +5804,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>626</v>
       </c>
@@ -5681,7 +5815,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5692,7 +5826,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5704,7 +5838,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5716,7 +5850,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5727,7 +5861,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
         <v>9</v>
       </c>
@@ -5738,7 +5872,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>627</v>
       </c>
@@ -5749,7 +5883,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>629</v>
       </c>
@@ -5760,7 +5894,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>630</v>
       </c>
@@ -5771,7 +5905,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5782,7 +5916,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>631</v>
       </c>
@@ -5793,7 +5927,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>632</v>
       </c>
@@ -5804,7 +5938,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>633</v>
       </c>
@@ -5815,7 +5949,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>634</v>
       </c>
@@ -5826,7 +5960,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5837,19 +5971,19 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>635</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46249.324131944442</v>
+        <v>46253.597737731485</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>1316</v>
       </c>
@@ -5860,7 +5994,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="38" t="s">
         <v>1310</v>
       </c>
@@ -5872,7 +6006,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
         <v>1317</v>
       </c>
@@ -5884,7 +6018,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>624</v>
       </c>
@@ -5895,7 +6029,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>636</v>
       </c>
@@ -5906,7 +6040,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>641</v>
       </c>
@@ -5917,7 +6051,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>643</v>
       </c>
@@ -5928,7 +6062,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="42" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="42" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="38" t="s">
         <v>1302</v>
       </c>
@@ -5939,143 +6073,143 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="38" t="s">
         <v>1477</v>
       </c>
-      <c r="B27" s="66" t="s">
+      <c r="B27" s="65" t="s">
         <v>1478</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="38" t="s">
         <v>1479</v>
       </c>
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="66" t="s">
         <v>1480</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="38" t="s">
         <v>1481</v>
       </c>
-      <c r="B29" s="67" t="s">
+      <c r="B29" s="66" t="s">
         <v>1482</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="38" t="s">
         <v>1483</v>
       </c>
-      <c r="B30" s="68" t="s">
+      <c r="B30" s="67" t="s">
         <v>1484</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="38" t="s">
         <v>1485</v>
       </c>
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="67" t="s">
         <v>1486</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="38" t="s">
         <v>1487</v>
       </c>
-      <c r="B32" s="68" t="s">
+      <c r="B32" s="67" t="s">
         <v>1488</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="38" t="s">
         <v>1489</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="69" t="s">
         <v>1490</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="38" t="s">
         <v>1491</v>
       </c>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="69" t="s">
         <v>1492</v>
       </c>
       <c r="C34" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="38" t="s">
         <v>1493</v>
       </c>
-      <c r="B35" s="68" t="s">
+      <c r="B35" s="67" t="s">
         <v>1494</v>
       </c>
       <c r="C35" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="38" t="s">
         <v>1495</v>
       </c>
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="69" t="s">
         <v>1496</v>
       </c>
       <c r="C36" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="69" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="38" t="s">
         <v>1497</v>
       </c>
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="67" t="s">
         <v>1498</v>
       </c>
       <c r="C37" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>1499</v>
       </c>
-      <c r="B38" s="71" t="s">
+      <c r="B38" s="70" t="s">
         <v>1500</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>1307</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="73" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="72" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="38" t="s">
         <v>1501</v>
       </c>
-      <c r="B39" s="72" t="s">
+      <c r="B39" s="71" t="s">
         <v>1502</v>
       </c>
       <c r="C39" s="41" t="s">
@@ -6097,35 +6231,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA34"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC34"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.09765625" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.8984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.33203125" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="61.796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.69921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="33" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="35.8984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="56.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="61.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.6640625" customWidth="1"/>
+    <col min="24" max="24" width="7.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.83203125" style="33" customWidth="1"/>
+    <col min="27" max="27" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.6640625" style="33" customWidth="1"/>
+    <col min="29" max="29" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="37" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>1251</v>
       </c>
@@ -6177,38 +6313,44 @@
       <c r="Q1" s="11" t="s">
         <v>1271</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="36" t="s">
+        <v>1301</v>
+      </c>
+      <c r="S1" s="11" t="s">
         <v>1295</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="T1" s="11" t="s">
         <v>1253</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="U1" s="11" t="s">
         <v>1272</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>1255</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>1254</v>
       </c>
-      <c r="W1" s="65" t="s">
+      <c r="X1" s="64" t="s">
         <v>1273</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>1299</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
+        <v>1518</v>
+      </c>
+      <c r="AA1" s="11" t="s">
         <v>1300</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AC1" s="11" t="s">
         <v>1274</v>
       </c>
-      <c r="AA1" s="36" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -6264,42 +6406,48 @@
       <c r="Q2" s="57" t="s">
         <v>1439</v>
       </c>
-      <c r="R2" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S2" s="58" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="59" t="s">
+        <v>1440</v>
+      </c>
+      <c r="S2" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T2" s="58" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="58" t="str">
+      <c r="U2" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="57" t="str">
+      <c r="V2" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="W2" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W2" s="64" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="63" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="Y2" s="37" t="s">
         <v>1513</v>
       </c>
-      <c r="Y2" s="37" t="s">
+      <c r="Z2" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA2" s="37" t="s">
         <v>1514</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="AB2" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC2" s="37" t="s">
         <v>1329</v>
       </c>
-      <c r="AA2" s="59" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -6355,42 +6503,48 @@
       <c r="Q3" s="57" t="s">
         <v>1442</v>
       </c>
-      <c r="R3" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S3" s="58" t="str">
+      <c r="R3" s="59" t="s">
+        <v>1443</v>
+      </c>
+      <c r="S3" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T3" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="58" t="str">
+      <c r="U3" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="57" t="str">
+      <c r="V3" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="37" t="s">
+      <c r="W3" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W3" s="64" t="str">
+      <c r="X3" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="37" t="s">
+      <c r="Y3" s="37" t="s">
         <v>1515</v>
       </c>
-      <c r="Y3" s="37" t="s">
+      <c r="Z3" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA3" s="37" t="s">
         <v>1516</v>
       </c>
-      <c r="Z3" s="37" t="s">
+      <c r="AB3" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC3" s="37" t="s">
         <v>1330</v>
       </c>
-      <c r="AA3" s="59" t="s">
-        <v>1443</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -6446,42 +6600,48 @@
       <c r="Q4" s="57" t="s">
         <v>1445</v>
       </c>
-      <c r="R4" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S4" s="58" t="str">
+      <c r="R4" s="59" t="s">
+        <v>1446</v>
+      </c>
+      <c r="S4" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T4" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="58" t="str">
+      <c r="U4" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="57" t="str">
+      <c r="V4" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="37" t="s">
+      <c r="W4" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W4" s="64" t="str">
+      <c r="X4" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="37" t="s">
+      <c r="Y4" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Y4" s="37" t="s">
+      <c r="Z4" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA4" s="37" t="s">
         <v>1507</v>
       </c>
-      <c r="Z4" s="37" t="s">
+      <c r="AB4" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC4" s="37" t="s">
         <v>1331</v>
       </c>
-      <c r="AA4" s="59" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -6537,42 +6697,48 @@
       <c r="Q5" s="57" t="s">
         <v>1448</v>
       </c>
-      <c r="R5" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S5" s="58" t="str">
+      <c r="R5" s="59" t="s">
+        <v>1449</v>
+      </c>
+      <c r="S5" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T5" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="58" t="str">
+      <c r="U5" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="57" t="str">
+      <c r="V5" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="37" t="s">
+      <c r="W5" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W5" s="64" t="str">
+      <c r="X5" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="37" t="s">
+      <c r="Y5" s="37" t="s">
         <v>1508</v>
       </c>
-      <c r="Y5" s="37" t="s">
+      <c r="Z5" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA5" s="37" t="s">
         <v>1509</v>
       </c>
-      <c r="Z5" s="37" t="s">
+      <c r="AB5" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC5" s="37" t="s">
         <v>1332</v>
       </c>
-      <c r="AA5" s="59" t="s">
-        <v>1449</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -6628,42 +6794,48 @@
       <c r="Q6" s="57" t="s">
         <v>1451</v>
       </c>
-      <c r="R6" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S6" s="58" t="str">
+      <c r="R6" s="59" t="s">
+        <v>1452</v>
+      </c>
+      <c r="S6" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T6" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="58" t="str">
+      <c r="U6" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="57" t="str">
+      <c r="V6" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="37" t="s">
+      <c r="W6" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W6" s="64" t="str">
+      <c r="X6" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="37" t="s">
+      <c r="Y6" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Y6" s="37" t="s">
+      <c r="Z6" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA6" s="37" t="s">
         <v>1507</v>
       </c>
-      <c r="Z6" s="37" t="s">
+      <c r="AB6" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC6" s="37" t="s">
         <v>1333</v>
       </c>
-      <c r="AA6" s="59" t="s">
-        <v>1452</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -6719,42 +6891,48 @@
       <c r="Q7" s="57" t="s">
         <v>1454</v>
       </c>
-      <c r="R7" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S7" s="58" t="str">
+      <c r="R7" s="59" t="s">
+        <v>1455</v>
+      </c>
+      <c r="S7" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T7" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="58" t="str">
+      <c r="U7" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="57" t="str">
+      <c r="V7" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="37" t="s">
+      <c r="W7" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W7" s="64" t="str">
+      <c r="X7" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y7" s="37" t="s">
         <v>1506</v>
       </c>
       <c r="Z7" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA7" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB7" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC7" s="37" t="s">
         <v>1334</v>
       </c>
-      <c r="AA7" s="59" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -6810,42 +6988,48 @@
       <c r="Q8" s="57" t="s">
         <v>1457</v>
       </c>
-      <c r="R8" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S8" s="58" t="str">
+      <c r="R8" s="59" t="s">
+        <v>1458</v>
+      </c>
+      <c r="S8" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T8" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="58" t="str">
+      <c r="U8" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="57" t="str">
+      <c r="V8" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="37" t="s">
+      <c r="W8" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W8" s="64" t="str">
+      <c r="X8" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y8" s="37" t="s">
         <v>1506</v>
       </c>
       <c r="Z8" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA8" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB8" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC8" s="37" t="s">
         <v>1335</v>
       </c>
-      <c r="AA8" s="59" t="s">
-        <v>1458</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -6901,42 +7085,48 @@
       <c r="Q9" s="57" t="s">
         <v>1460</v>
       </c>
-      <c r="R9" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S9" s="58" t="str">
+      <c r="R9" s="59" t="s">
+        <v>1461</v>
+      </c>
+      <c r="S9" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T9" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="58" t="str">
+      <c r="U9" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="57" t="str">
+      <c r="V9" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="37" t="s">
+      <c r="W9" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W9" s="64" t="str">
+      <c r="X9" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y9" s="37" t="s">
         <v>1506</v>
       </c>
       <c r="Z9" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA9" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB9" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC9" s="37" t="s">
         <v>1243</v>
       </c>
-      <c r="AA9" s="59" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -6992,42 +7182,48 @@
       <c r="Q10" s="57" t="s">
         <v>1463</v>
       </c>
-      <c r="R10" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S10" s="58" t="str">
+      <c r="R10" s="59" t="s">
+        <v>1464</v>
+      </c>
+      <c r="S10" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T10" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="58" t="str">
+      <c r="U10" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="57" t="str">
+      <c r="V10" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="37" t="s">
+      <c r="W10" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W10" s="64" t="str">
+      <c r="X10" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y10" s="37" t="s">
         <v>1506</v>
       </c>
       <c r="Z10" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA10" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB10" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC10" s="37" t="s">
         <v>1336</v>
       </c>
-      <c r="AA10" s="59" t="s">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -7083,42 +7279,48 @@
       <c r="Q11" s="57" t="s">
         <v>1466</v>
       </c>
-      <c r="R11" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S11" s="58" t="str">
+      <c r="R11" s="59" t="s">
+        <v>1467</v>
+      </c>
+      <c r="S11" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T11" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="58" t="str">
+      <c r="U11" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="57" t="str">
+      <c r="V11" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="37" t="s">
+      <c r="W11" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W11" s="64" t="str">
+      <c r="X11" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y11" s="37" t="s">
         <v>1506</v>
       </c>
       <c r="Z11" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA11" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB11" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC11" s="37" t="s">
         <v>1337</v>
       </c>
-      <c r="AA11" s="59" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -7174,42 +7376,48 @@
       <c r="Q12" s="57" t="s">
         <v>1469</v>
       </c>
-      <c r="R12" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S12" s="58" t="str">
+      <c r="R12" s="59" t="s">
+        <v>1470</v>
+      </c>
+      <c r="S12" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T12" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="58" t="str">
+      <c r="U12" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="57" t="str">
+      <c r="V12" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="37" t="s">
+      <c r="W12" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W12" s="64" t="str">
+      <c r="X12" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="37" t="s">
+      <c r="Y12" s="37" t="s">
         <v>1510</v>
       </c>
-      <c r="Y12" s="37" t="s">
+      <c r="Z12" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA12" s="37" t="s">
         <v>1517</v>
       </c>
-      <c r="Z12" s="37" t="s">
+      <c r="AB12" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC12" s="37" t="s">
         <v>1338</v>
       </c>
-      <c r="AA12" s="59" t="s">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -7265,42 +7473,48 @@
       <c r="Q13" s="57" t="s">
         <v>1472</v>
       </c>
-      <c r="R13" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S13" s="58" t="str">
+      <c r="R13" s="59" t="s">
+        <v>1473</v>
+      </c>
+      <c r="S13" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T13" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="58" t="str">
+      <c r="U13" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="57" t="str">
+      <c r="V13" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="37" t="s">
+      <c r="W13" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W13" s="64" t="str">
+      <c r="X13" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="37" t="s">
+      <c r="Y13" s="37" t="s">
         <v>1510</v>
       </c>
-      <c r="Y13" s="37" t="s">
+      <c r="Z13" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA13" s="37" t="s">
         <v>1517</v>
       </c>
-      <c r="Z13" s="37" t="s">
+      <c r="AB13" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC13" s="37" t="s">
         <v>1339</v>
       </c>
-      <c r="AA13" s="59" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -7356,42 +7570,48 @@
       <c r="Q14" s="57" t="s">
         <v>1475</v>
       </c>
-      <c r="R14" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S14" s="58" t="str">
+      <c r="R14" s="59" t="s">
+        <v>1476</v>
+      </c>
+      <c r="S14" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T14" s="58" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="58" t="str">
+      <c r="U14" s="58" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="57" t="str">
+      <c r="V14" s="57" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="37" t="s">
+      <c r="W14" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W14" s="64" t="str">
+      <c r="X14" s="63" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="74" t="s">
+      <c r="Y14" s="73" t="s">
         <v>1511</v>
       </c>
-      <c r="Y14" s="75" t="s">
+      <c r="Z14" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA14" s="74" t="s">
         <v>1512</v>
       </c>
-      <c r="Z14" s="37" t="s">
+      <c r="AB14" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC14" s="37" t="s">
         <v>1340</v>
       </c>
-      <c r="AA14" s="59" t="s">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -7444,47 +7664,51 @@
       <c r="P15" s="57" t="s">
         <v>1433</v>
       </c>
-      <c r="Q15" s="57" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Herramientas de diseño, gráficos y hardware de TI</v>
-      </c>
-      <c r="R15" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S15" s="58" t="str">
-        <f t="shared" ref="S15:U15" si="6">SUBSTITUTE(C15, "_", " ")</f>
+      <c r="Q15" s="57" t="s">
+        <v>1546</v>
+      </c>
+      <c r="R15" s="59" t="s">
+        <v>1527</v>
+      </c>
+      <c r="S15" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T15" s="58" t="str">
+        <f t="shared" ref="T15:V15" si="6">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="58" t="str">
+      <c r="U15" s="58" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="57" t="str">
+      <c r="V15" s="57" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V15" s="37" t="s">
+      <c r="W15" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W15" s="64" t="str">
-        <f t="shared" ref="W15:W34" si="7">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="63" t="str">
+        <f t="shared" ref="X15:X34" si="7">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
-      </c>
-      <c r="X15" s="37" t="s">
-        <v>1506</v>
       </c>
       <c r="Y15" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z15" s="63" t="s">
+      <c r="Z15" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA15" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB15" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC15" s="75" t="s">
         <v>1362</v>
       </c>
-      <c r="AA15" s="59" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Design, Graphic, and IT Hardware Tools</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -7537,47 +7761,51 @@
       <c r="P16" s="57" t="s">
         <v>1436</v>
       </c>
-      <c r="Q16" s="57" t="str">
-        <f>_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>Herramientas de Red TI</v>
-      </c>
-      <c r="R16" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S16" s="58" t="str">
-        <f t="shared" ref="S16" si="12">SUBSTITUTE(C16, "_", " ")</f>
+      <c r="Q16" s="57" t="s">
+        <v>1547</v>
+      </c>
+      <c r="R16" s="59" t="s">
+        <v>1528</v>
+      </c>
+      <c r="S16" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T16" s="58" t="str">
+        <f t="shared" ref="T16" si="12">SUBSTITUTE(C16, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="58" t="str">
-        <f t="shared" ref="T16" si="13">SUBSTITUTE(D16, "_", " ")</f>
+      <c r="U16" s="58" t="str">
+        <f t="shared" ref="U16" si="13">SUBSTITUTE(D16, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="57" t="str">
-        <f t="shared" ref="U16" si="14">SUBSTITUTE(E16, "_", " ")</f>
+      <c r="V16" s="57" t="str">
+        <f t="shared" ref="V16" si="14">SUBSTITUTE(E16, "_", " ")</f>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V16" s="37" t="s">
+      <c r="W16" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W16" s="64" t="str">
+      <c r="X16" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y16" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z16" s="63" t="s">
+      <c r="Z16" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA16" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB16" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC16" s="75" t="s">
         <v>1437</v>
       </c>
-      <c r="AA16" s="59" t="str">
-        <f>_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>IT Network Tools</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -7630,47 +7858,51 @@
       <c r="P17" s="57" t="s">
         <v>1434</v>
       </c>
-      <c r="Q17" s="57" t="str">
-        <f t="shared" ref="Q17:Q26" si="15">_xlfn.TRANSLATE(P17,"pt","es")</f>
-        <v>Herramientas de software para diseño, gráficos o gestión</v>
-      </c>
-      <c r="R17" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S17" s="58" t="str">
-        <f t="shared" ref="S17:S26" si="16">SUBSTITUTE(C17, "_", " ")</f>
+      <c r="Q17" s="57" t="s">
+        <v>1520</v>
+      </c>
+      <c r="R17" s="59" t="s">
+        <v>1529</v>
+      </c>
+      <c r="S17" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T17" s="58" t="str">
+        <f t="shared" ref="T17:T26" si="15">SUBSTITUTE(C17, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="58" t="str">
-        <f t="shared" ref="T17:T26" si="17">SUBSTITUTE(D17, "_", " ")</f>
+      <c r="U17" s="58" t="str">
+        <f t="shared" ref="U17:U26" si="16">SUBSTITUTE(D17, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="57" t="str">
-        <f t="shared" ref="U17:U26" si="18">SUBSTITUTE(E17, "_", " ")</f>
+      <c r="V17" s="57" t="str">
+        <f t="shared" ref="V17:V26" si="17">SUBSTITUTE(E17, "_", " ")</f>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V17" s="37" t="s">
+      <c r="W17" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W17" s="64" t="str">
+      <c r="X17" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y17" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z17" s="63" t="s">
+      <c r="Z17" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA17" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB17" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC17" s="75" t="s">
         <v>1363</v>
       </c>
-      <c r="AA17" s="59" t="str">
-        <f t="shared" ref="AA17:AA34" si="19">_xlfn.TRANSLATE(P17,"pt","en")</f>
-        <v>Software tools for design, graphics or management</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -7723,47 +7955,51 @@
       <c r="P18" s="57" t="s">
         <v>1384</v>
       </c>
-      <c r="Q18" s="57" t="str">
+      <c r="Q18" s="57" t="s">
+        <v>1521</v>
+      </c>
+      <c r="R18" s="59" t="s">
+        <v>1530</v>
+      </c>
+      <c r="S18" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T18" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de medición</v>
-      </c>
-      <c r="R18" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S18" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U18" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T18" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V18" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U18" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V18" s="37" t="s">
+      <c r="W18" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W18" s="64" t="str">
+      <c r="X18" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y18" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z18" s="63" t="s">
+      <c r="Z18" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA18" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB18" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC18" s="75" t="s">
         <v>1364</v>
       </c>
-      <c r="AA18" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Measurement Tools</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -7816,47 +8052,51 @@
       <c r="P19" s="57" t="s">
         <v>1422</v>
       </c>
-      <c r="Q19" s="57" t="str">
+      <c r="Q19" s="57" t="s">
+        <v>1548</v>
+      </c>
+      <c r="R19" s="59" t="s">
+        <v>1531</v>
+      </c>
+      <c r="S19" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T19" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de monitorización</v>
-      </c>
-      <c r="R19" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S19" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U19" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T19" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V19" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U19" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V19" s="37" t="s">
+      <c r="W19" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W19" s="64" t="str">
+      <c r="X19" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y19" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z19" s="63" t="s">
+      <c r="Z19" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA19" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB19" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC19" s="75" t="s">
         <v>1365</v>
       </c>
-      <c r="AA19" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Monitoring Tools</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -7909,47 +8149,51 @@
       <c r="P20" s="57" t="s">
         <v>1385</v>
       </c>
-      <c r="Q20" s="57" t="str">
+      <c r="Q20" s="57" t="s">
+        <v>1549</v>
+      </c>
+      <c r="R20" s="59" t="s">
+        <v>1532</v>
+      </c>
+      <c r="S20" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T20" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de prueba</v>
-      </c>
-      <c r="R20" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S20" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U20" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T20" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V20" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U20" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V20" s="37" t="s">
+      <c r="W20" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W20" s="64" t="str">
+      <c r="X20" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y20" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z20" s="63" t="s">
+      <c r="Z20" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA20" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB20" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC20" s="75" t="s">
         <v>1366</v>
       </c>
-      <c r="AA20" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Testing Tools</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -8002,47 +8246,51 @@
       <c r="P21" s="57" t="s">
         <v>1386</v>
       </c>
-      <c r="Q21" s="57" t="str">
+      <c r="Q21" s="57" t="s">
+        <v>1550</v>
+      </c>
+      <c r="R21" s="59" t="s">
+        <v>1533</v>
+      </c>
+      <c r="S21" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T21" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de construcción</v>
-      </c>
-      <c r="R21" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S21" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U21" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T21" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V21" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U21" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V21" s="37" t="s">
+      <c r="W21" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W21" s="64" t="str">
+      <c r="X21" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y21" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z21" s="63" t="s">
+      <c r="Z21" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA21" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB21" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC21" s="75" t="s">
         <v>1367</v>
       </c>
-      <c r="AA21" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Construction Tools</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -8095,47 +8343,51 @@
       <c r="P22" s="57" t="s">
         <v>1423</v>
       </c>
-      <c r="Q22" s="57" t="str">
+      <c r="Q22" s="57" t="s">
+        <v>1551</v>
+      </c>
+      <c r="R22" s="59" t="s">
+        <v>1534</v>
+      </c>
+      <c r="S22" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T22" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de acabado</v>
-      </c>
-      <c r="R22" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S22" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U22" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T22" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V22" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U22" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V22" s="37" t="s">
+      <c r="W22" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W22" s="64" t="str">
+      <c r="X22" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y22" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z22" s="63" t="s">
+      <c r="Z22" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA22" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB22" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC22" s="75" t="s">
         <v>1407</v>
       </c>
-      <c r="AA22" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Finishing Tools</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -8188,47 +8440,51 @@
       <c r="P23" s="57" t="s">
         <v>1424</v>
       </c>
-      <c r="Q23" s="57" t="str">
+      <c r="Q23" s="57" t="s">
+        <v>1552</v>
+      </c>
+      <c r="R23" s="59" t="s">
+        <v>1535</v>
+      </c>
+      <c r="S23" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T23" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de transporte</v>
-      </c>
-      <c r="R23" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S23" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U23" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T23" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V23" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U23" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V23" s="37" t="s">
+      <c r="W23" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W23" s="64" t="str">
+      <c r="X23" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y23" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z23" s="63" t="s">
+      <c r="Z23" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA23" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB23" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC23" s="75" t="s">
         <v>1408</v>
       </c>
-      <c r="AA23" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Transportation Tools</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="55">
         <v>24</v>
       </c>
@@ -8281,47 +8537,51 @@
       <c r="P24" s="57" t="s">
         <v>1428</v>
       </c>
-      <c r="Q24" s="57" t="str">
+      <c r="Q24" s="57" t="s">
+        <v>1522</v>
+      </c>
+      <c r="R24" s="59" t="s">
+        <v>1536</v>
+      </c>
+      <c r="S24" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T24" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas eléctricas</v>
-      </c>
-      <c r="R24" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S24" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U24" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T24" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V24" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U24" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V24" s="37" t="s">
+      <c r="W24" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W24" s="64" t="str">
+      <c r="X24" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="X24" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y24" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z24" s="63" t="s">
+      <c r="Z24" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA24" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB24" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC24" s="75" t="s">
         <v>1409</v>
       </c>
-      <c r="AA24" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Power Tools</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="55">
         <v>25</v>
       </c>
@@ -8374,47 +8634,51 @@
       <c r="P25" s="57" t="s">
         <v>1425</v>
       </c>
-      <c r="Q25" s="57" t="str">
+      <c r="Q25" s="57" t="s">
+        <v>1523</v>
+      </c>
+      <c r="R25" s="59" t="s">
+        <v>1537</v>
+      </c>
+      <c r="S25" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T25" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de control</v>
-      </c>
-      <c r="R25" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S25" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U25" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T25" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V25" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U25" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V25" s="37" t="s">
+      <c r="W25" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W25" s="64" t="str">
+      <c r="X25" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="X25" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y25" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z25" s="63" t="s">
+      <c r="Z25" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA25" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB25" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC25" s="75" t="s">
         <v>1410</v>
       </c>
-      <c r="AA25" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Control Tools</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="55">
         <v>26</v>
       </c>
@@ -8467,47 +8731,51 @@
       <c r="P26" s="57" t="s">
         <v>1429</v>
       </c>
-      <c r="Q26" s="57" t="str">
+      <c r="Q26" s="57" t="s">
+        <v>1553</v>
+      </c>
+      <c r="R26" s="59" t="s">
+        <v>1538</v>
+      </c>
+      <c r="S26" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T26" s="58" t="str">
         <f t="shared" si="15"/>
-        <v>Herramientas de protección individual individual (EPP)</v>
-      </c>
-      <c r="R26" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S26" s="58" t="str">
+        <v>Normativos</v>
+      </c>
+      <c r="U26" s="58" t="str">
         <f t="shared" si="16"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T26" s="58" t="str">
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V26" s="57" t="str">
         <f t="shared" si="17"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U26" s="57" t="str">
-        <f t="shared" si="18"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V26" s="37" t="s">
+      <c r="W26" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W26" s="64" t="str">
+      <c r="X26" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="X26" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y26" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z26" s="63" t="s">
+      <c r="Z26" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA26" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB26" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC26" s="75" t="s">
         <v>1411</v>
       </c>
-      <c r="AA26" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>PPE Personal Protective Tools</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="55">
         <v>27</v>
       </c>
@@ -8542,65 +8810,69 @@
         <v>638</v>
       </c>
       <c r="L27" s="57" t="str">
-        <f t="shared" ref="L27:L34" si="20">CONCATENATE("", C27)</f>
+        <f t="shared" ref="L27:L34" si="18">CONCATENATE("", C27)</f>
         <v>Normativos</v>
       </c>
       <c r="M27" s="57" t="str">
-        <f t="shared" ref="M27:M34" si="21">CONCATENATE("", D27)</f>
+        <f t="shared" ref="M27:M34" si="19">CONCATENATE("", D27)</f>
         <v>NBR.Temáticas</v>
       </c>
       <c r="N27" s="57" t="str">
-        <f t="shared" ref="N27:N34" si="22">CONCATENATE("", E27)</f>
+        <f t="shared" ref="N27:N34" si="20">CONCATENATE("", E27)</f>
         <v>NBR.Equipamentos</v>
       </c>
       <c r="O27" s="57" t="str">
-        <f t="shared" ref="O27:O34" si="23">F27</f>
+        <f t="shared" ref="O27:O34" si="21">F27</f>
         <v>NBR.Q.Ferramenta.de.Construção.Geral</v>
       </c>
       <c r="P27" s="57" t="s">
         <v>1426</v>
       </c>
-      <c r="Q27" s="57" t="str">
-        <f t="shared" ref="Q27:Q34" si="24">_xlfn.TRANSLATE(P27,"pt","es")</f>
-        <v>Herramientas generales de construcción</v>
-      </c>
-      <c r="R27" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S27" s="58" t="str">
-        <f t="shared" ref="S27:S34" si="25">SUBSTITUTE(C27, "_", " ")</f>
+      <c r="Q27" s="57" t="s">
+        <v>1554</v>
+      </c>
+      <c r="R27" s="59" t="s">
+        <v>1539</v>
+      </c>
+      <c r="S27" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T27" s="58" t="str">
+        <f t="shared" ref="T27:T34" si="22">SUBSTITUTE(C27, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T27" s="58" t="str">
-        <f t="shared" ref="T27:T34" si="26">SUBSTITUTE(D27, "_", " ")</f>
+      <c r="U27" s="58" t="str">
+        <f t="shared" ref="U27:U34" si="23">SUBSTITUTE(D27, "_", " ")</f>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U27" s="57" t="str">
-        <f t="shared" ref="U27:U34" si="27">SUBSTITUTE(E27, "_", " ")</f>
+      <c r="V27" s="57" t="str">
+        <f t="shared" ref="V27:V34" si="24">SUBSTITUTE(E27, "_", " ")</f>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V27" s="37" t="s">
+      <c r="W27" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W27" s="64" t="str">
+      <c r="X27" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="X27" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y27" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z27" s="63" t="s">
+      <c r="Z27" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA27" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB27" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC27" s="75" t="s">
         <v>1412</v>
       </c>
-      <c r="AA27" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>General Construction Tools</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="55">
         <v>28</v>
       </c>
@@ -8635,65 +8907,69 @@
         <v>638</v>
       </c>
       <c r="L28" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M28" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N28" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M28" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O28" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N28" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O28" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Ferramenta.de.Canteiro</v>
       </c>
       <c r="P28" s="57" t="s">
         <v>1427</v>
       </c>
-      <c r="Q28" s="57" t="str">
+      <c r="Q28" s="57" t="s">
+        <v>1555</v>
+      </c>
+      <c r="R28" s="59" t="s">
+        <v>1540</v>
+      </c>
+      <c r="S28" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T28" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U28" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V28" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Herramientas para obras</v>
-      </c>
-      <c r="R28" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S28" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T28" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U28" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V28" s="37" t="s">
+      <c r="W28" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W28" s="64" t="str">
+      <c r="X28" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-28</v>
       </c>
-      <c r="X28" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y28" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z28" s="63" t="s">
+      <c r="Z28" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA28" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB28" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC28" s="75" t="s">
         <v>1413</v>
       </c>
-      <c r="AA28" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Construction Site Tools</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="55">
         <v>29</v>
       </c>
@@ -8728,65 +9004,69 @@
         <v>638</v>
       </c>
       <c r="L29" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M29" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N29" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M29" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O29" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N29" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O29" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Ferramenta.de.Suporte</v>
       </c>
       <c r="P29" s="57" t="s">
         <v>1421</v>
       </c>
-      <c r="Q29" s="57" t="str">
+      <c r="Q29" s="57" t="s">
+        <v>1556</v>
+      </c>
+      <c r="R29" s="59" t="s">
+        <v>1541</v>
+      </c>
+      <c r="S29" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T29" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U29" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V29" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Herramientas de soporte</v>
-      </c>
-      <c r="R29" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S29" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T29" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U29" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V29" s="37" t="s">
+      <c r="W29" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W29" s="64" t="str">
+      <c r="X29" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-29</v>
       </c>
-      <c r="X29" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y29" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z29" s="63" t="s">
+      <c r="Z29" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA29" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB29" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC29" s="75" t="s">
         <v>1414</v>
       </c>
-      <c r="AA29" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Support Tools</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="55">
         <v>30</v>
       </c>
@@ -8821,65 +9101,69 @@
         <v>638</v>
       </c>
       <c r="L30" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M30" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N30" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M30" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O30" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N30" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O30" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Bombear.Tunelar</v>
       </c>
       <c r="P30" s="57" t="s">
         <v>1416</v>
       </c>
-      <c r="Q30" s="57" t="str">
+      <c r="Q30" s="57" t="s">
+        <v>1557</v>
+      </c>
+      <c r="R30" s="59" t="s">
+        <v>1542</v>
+      </c>
+      <c r="S30" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T30" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U30" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V30" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Equipos de bombeo y túneles</v>
-      </c>
-      <c r="R30" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S30" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T30" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U30" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V30" s="37" t="s">
+      <c r="W30" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W30" s="64" t="str">
+      <c r="X30" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-30</v>
       </c>
-      <c r="X30" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y30" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z30" s="63" t="s">
+      <c r="Z30" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA30" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB30" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC30" s="75" t="s">
         <v>1415</v>
       </c>
-      <c r="AA30" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Pumping and Tunneling Equipment</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="55">
         <v>31</v>
       </c>
@@ -8914,65 +9198,69 @@
         <v>638</v>
       </c>
       <c r="L31" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M31" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N31" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M31" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O31" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N31" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O31" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Produzir.Concreto</v>
       </c>
       <c r="P31" s="57" t="s">
         <v>1417</v>
       </c>
-      <c r="Q31" s="57" t="str">
+      <c r="Q31" s="57" t="s">
+        <v>1558</v>
+      </c>
+      <c r="R31" s="59" t="s">
+        <v>1543</v>
+      </c>
+      <c r="S31" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T31" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U31" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V31" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Equipos de producción de hormigón</v>
-      </c>
-      <c r="R31" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S31" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T31" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U31" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V31" s="37" t="s">
+      <c r="W31" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W31" s="64" t="str">
+      <c r="X31" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-31</v>
       </c>
-      <c r="X31" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y31" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z31" s="63" t="s">
+      <c r="Z31" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA31" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB31" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC31" s="75" t="s">
         <v>1368</v>
       </c>
-      <c r="AA31" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Concrete Production Equipment</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="55">
         <v>32</v>
       </c>
@@ -9007,65 +9295,69 @@
         <v>638</v>
       </c>
       <c r="L32" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M32" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N32" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M32" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O32" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N32" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O32" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Perfurar.Cortar</v>
       </c>
       <c r="P32" s="57" t="s">
         <v>1418</v>
       </c>
-      <c r="Q32" s="57" t="str">
+      <c r="Q32" s="57" t="s">
+        <v>1559</v>
+      </c>
+      <c r="R32" s="59" t="s">
+        <v>1526</v>
+      </c>
+      <c r="S32" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T32" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U32" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V32" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Equipos de perforación y corte</v>
-      </c>
-      <c r="R32" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S32" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T32" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U32" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V32" s="37" t="s">
+      <c r="W32" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W32" s="64" t="str">
+      <c r="X32" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-32</v>
       </c>
-      <c r="X32" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y32" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z32" s="63" t="s">
+      <c r="Z32" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA32" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB32" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC32" s="75" t="s">
         <v>1369</v>
       </c>
-      <c r="AA32" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Drilling &amp; Cutting Equipment</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="55">
         <v>33</v>
       </c>
@@ -9100,65 +9392,69 @@
         <v>638</v>
       </c>
       <c r="L33" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M33" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N33" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M33" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O33" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N33" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O33" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Demolir.Terraplanar</v>
       </c>
       <c r="P33" s="57" t="s">
         <v>1419</v>
       </c>
-      <c r="Q33" s="57" t="str">
+      <c r="Q33" s="57" t="s">
+        <v>1524</v>
+      </c>
+      <c r="R33" s="59" t="s">
+        <v>1544</v>
+      </c>
+      <c r="S33" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T33" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U33" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V33" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Equipos para demolición y movimiento de tierras</v>
-      </c>
-      <c r="R33" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S33" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T33" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U33" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V33" s="37" t="s">
+      <c r="W33" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W33" s="64" t="str">
+      <c r="X33" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-33</v>
       </c>
-      <c r="X33" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y33" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z33" s="63" t="s">
+      <c r="Z33" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA33" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB33" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC33" s="75" t="s">
         <v>1370</v>
       </c>
-      <c r="AA33" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Equipment for Demolition and Earthmoving</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:29" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="55">
         <v>34</v>
       </c>
@@ -9193,81 +9489,90 @@
         <v>638</v>
       </c>
       <c r="L34" s="57" t="str">
+        <f t="shared" si="18"/>
+        <v>Normativos</v>
+      </c>
+      <c r="M34" s="57" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="N34" s="57" t="str">
         <f t="shared" si="20"/>
-        <v>Normativos</v>
-      </c>
-      <c r="M34" s="57" t="str">
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O34" s="57" t="str">
         <f t="shared" si="21"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="N34" s="57" t="str">
-        <f t="shared" si="22"/>
-        <v>NBR.Equipamentos</v>
-      </c>
-      <c r="O34" s="57" t="str">
-        <f t="shared" si="23"/>
         <v>NBR.Q.Limpar.Fachada</v>
       </c>
       <c r="P34" s="57" t="s">
         <v>1420</v>
       </c>
-      <c r="Q34" s="57" t="str">
+      <c r="Q34" s="57" t="s">
+        <v>1525</v>
+      </c>
+      <c r="R34" s="59" t="s">
+        <v>1545</v>
+      </c>
+      <c r="S34" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="T34" s="58" t="str">
+        <f t="shared" si="22"/>
+        <v>Normativos</v>
+      </c>
+      <c r="U34" s="58" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Temáticas</v>
+      </c>
+      <c r="V34" s="57" t="str">
         <f t="shared" si="24"/>
-        <v>Equipos para la limpieza y mantenimiento de fachadas</v>
-      </c>
-      <c r="R34" s="37" t="s">
-        <v>638</v>
-      </c>
-      <c r="S34" s="58" t="str">
-        <f t="shared" si="25"/>
-        <v>Normativos</v>
-      </c>
-      <c r="T34" s="58" t="str">
-        <f t="shared" si="26"/>
-        <v>NBR.Temáticas</v>
-      </c>
-      <c r="U34" s="57" t="str">
-        <f t="shared" si="27"/>
         <v>NBR.Equipamentos</v>
       </c>
-      <c r="V34" s="37" t="s">
+      <c r="W34" s="37" t="s">
         <v>1328</v>
       </c>
-      <c r="W34" s="64" t="str">
+      <c r="X34" s="63" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-34</v>
       </c>
-      <c r="X34" s="37" t="s">
-        <v>1506</v>
-      </c>
       <c r="Y34" s="37" t="s">
         <v>1506</v>
       </c>
-      <c r="Z34" s="63" t="s">
+      <c r="Z34" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AA34" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AB34" s="37" t="s">
+        <v>1506</v>
+      </c>
+      <c r="AC34" s="75" t="s">
         <v>1371</v>
-      </c>
-      <c r="AA34" s="59" t="str">
-        <f t="shared" si="19"/>
-        <v>Equipment for Cleaning and Maintenance of Facades</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA34 A2:B34">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B34">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R34">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W1 A35:XFD1048576 AB1:XFD1 AB17:XFD26 AB27:XFD34" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AD1:XFD1 A35:P1048576 A1:P1 S35:Y1048576 AA35:AA1048576 AD17:XFD1048576 AC35:AC1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9276,13 +9581,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649E5DE9-BD63-4EDF-814C-ADC7DFAABB6E}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>1252</v>
       </c>
@@ -9347,7 +9652,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -9424,13 +9729,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBF1699-AA28-4D60-8669-5674605C36B3}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.69921875" customWidth="1"/>
-    <col min="2" max="3" width="14.69921875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="3" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="17">
         <v>1</v>
       </c>
@@ -9441,7 +9746,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -9461,31 +9766,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y610"/>
-  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.19921875" style="20" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.1640625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="20" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="20" customWidth="1"/>
     <col min="8" max="8" width="5" style="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.796875" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.19921875" style="20" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" style="20" customWidth="1"/>
-    <col min="12" max="12" width="5.796875" style="20" customWidth="1"/>
-    <col min="13" max="13" width="19.796875" style="20" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.1640625" style="20" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" style="20" customWidth="1"/>
+    <col min="12" max="12" width="5.83203125" style="20" customWidth="1"/>
+    <col min="13" max="13" width="19.83203125" style="20" customWidth="1"/>
     <col min="14" max="14" width="7" style="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.796875" style="20" customWidth="1"/>
-    <col min="17" max="17" width="5.296875" style="20" customWidth="1"/>
-    <col min="18" max="19" width="5.796875" style="20" customWidth="1"/>
-    <col min="20" max="25" width="4.69921875" style="20" customWidth="1"/>
-    <col min="26" max="16384" width="11.296875" style="2"/>
+    <col min="15" max="15" width="49.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.83203125" style="20" customWidth="1"/>
+    <col min="17" max="17" width="5.33203125" style="20" customWidth="1"/>
+    <col min="18" max="19" width="5.83203125" style="20" customWidth="1"/>
+    <col min="20" max="25" width="4.6640625" style="20" customWidth="1"/>
+    <col min="26" max="16384" width="11.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>637</v>
       </c>
@@ -9562,7 +9867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -9639,7 +9944,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -9716,7 +10021,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -9793,7 +10098,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -9870,7 +10175,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -9947,7 +10252,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -10024,7 +10329,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -10101,7 +10406,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -10178,7 +10483,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -10255,7 +10560,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -10332,7 +10637,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -10409,7 +10714,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -10486,7 +10791,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -10563,7 +10868,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -10640,7 +10945,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -10717,7 +11022,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -10794,7 +11099,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -10871,7 +11176,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -10948,7 +11253,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -11025,7 +11330,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -11102,7 +11407,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -11179,7 +11484,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -11256,7 +11561,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -11333,7 +11638,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -11410,7 +11715,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -11487,7 +11792,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -11564,7 +11869,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -11641,7 +11946,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -11718,7 +12023,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43">
         <v>30</v>
       </c>
@@ -11795,7 +12100,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43">
         <v>31</v>
       </c>
@@ -11872,7 +12177,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="43">
         <v>32</v>
       </c>
@@ -11949,7 +12254,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="43">
         <v>33</v>
       </c>
@@ -12026,7 +12331,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43">
         <v>34</v>
       </c>
@@ -12103,7 +12408,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43">
         <v>35</v>
       </c>
@@ -12180,7 +12485,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43">
         <v>36</v>
       </c>
@@ -12257,7 +12562,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="43">
         <v>37</v>
       </c>
@@ -12334,7 +12639,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="43">
         <v>38</v>
       </c>
@@ -12411,7 +12716,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="43">
         <v>39</v>
       </c>
@@ -12488,7 +12793,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="43">
         <v>40</v>
       </c>
@@ -12565,7 +12870,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="43">
         <v>41</v>
       </c>
@@ -12642,7 +12947,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="43">
         <v>42</v>
       </c>
@@ -12719,7 +13024,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="43">
         <v>43</v>
       </c>
@@ -12796,7 +13101,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="43">
         <v>44</v>
       </c>
@@ -12873,7 +13178,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="43">
         <v>45</v>
       </c>
@@ -12950,7 +13255,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="43">
         <v>46</v>
       </c>
@@ -13027,7 +13332,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="43">
         <v>47</v>
       </c>
@@ -13104,7 +13409,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="43">
         <v>48</v>
       </c>
@@ -13181,7 +13486,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="43">
         <v>49</v>
       </c>
@@ -13258,7 +13563,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="43">
         <v>50</v>
       </c>
@@ -13335,7 +13640,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="43">
         <v>51</v>
       </c>
@@ -13412,7 +13717,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="43">
         <v>52</v>
       </c>
@@ -13489,7 +13794,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="43">
         <v>53</v>
       </c>
@@ -13566,7 +13871,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="43">
         <v>54</v>
       </c>
@@ -13643,7 +13948,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="43">
         <v>55</v>
       </c>
@@ -13720,7 +14025,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="43">
         <v>56</v>
       </c>
@@ -13797,7 +14102,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="43">
         <v>57</v>
       </c>
@@ -13874,7 +14179,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="43">
         <v>58</v>
       </c>
@@ -13951,7 +14256,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="43">
         <v>59</v>
       </c>
@@ -14028,7 +14333,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="43">
         <v>60</v>
       </c>
@@ -14105,7 +14410,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="43">
         <v>61</v>
       </c>
@@ -14182,7 +14487,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="43">
         <v>62</v>
       </c>
@@ -14259,7 +14564,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="43">
         <v>63</v>
       </c>
@@ -14336,7 +14641,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="43">
         <v>64</v>
       </c>
@@ -14413,7 +14718,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="43">
         <v>65</v>
       </c>
@@ -14490,7 +14795,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="43">
         <v>66</v>
       </c>
@@ -14567,7 +14872,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="43">
         <v>67</v>
       </c>
@@ -14644,7 +14949,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="43">
         <v>68</v>
       </c>
@@ -14721,7 +15026,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="43">
         <v>69</v>
       </c>
@@ -14798,7 +15103,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="43">
         <v>70</v>
       </c>
@@ -14875,7 +15180,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="43">
         <v>71</v>
       </c>
@@ -14952,7 +15257,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="43">
         <v>72</v>
       </c>
@@ -15029,7 +15334,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="43">
         <v>73</v>
       </c>
@@ -15106,7 +15411,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="43">
         <v>74</v>
       </c>
@@ -15183,7 +15488,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="43">
         <v>75</v>
       </c>
@@ -15260,7 +15565,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="43">
         <v>76</v>
       </c>
@@ -15337,7 +15642,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="43">
         <v>77</v>
       </c>
@@ -15414,7 +15719,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="43">
         <v>78</v>
       </c>
@@ -15491,7 +15796,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="43">
         <v>79</v>
       </c>
@@ -15568,7 +15873,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="43">
         <v>80</v>
       </c>
@@ -15645,7 +15950,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="43">
         <v>81</v>
       </c>
@@ -15722,7 +16027,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="43">
         <v>82</v>
       </c>
@@ -15799,7 +16104,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="43">
         <v>83</v>
       </c>
@@ -15876,7 +16181,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="43">
         <v>84</v>
       </c>
@@ -15953,7 +16258,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="43">
         <v>85</v>
       </c>
@@ -16030,7 +16335,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="43">
         <v>86</v>
       </c>
@@ -16107,7 +16412,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="43">
         <v>87</v>
       </c>
@@ -16184,7 +16489,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="43">
         <v>88</v>
       </c>
@@ -16261,7 +16566,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="43">
         <v>89</v>
       </c>
@@ -16338,7 +16643,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="43">
         <v>90</v>
       </c>
@@ -16415,7 +16720,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="43">
         <v>91</v>
       </c>
@@ -16492,7 +16797,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="43">
         <v>92</v>
       </c>
@@ -16569,7 +16874,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="43">
         <v>93</v>
       </c>
@@ -16646,7 +16951,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="43">
         <v>94</v>
       </c>
@@ -16723,7 +17028,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="43">
         <v>95</v>
       </c>
@@ -16800,7 +17105,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="43">
         <v>96</v>
       </c>
@@ -16877,7 +17182,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="43">
         <v>97</v>
       </c>
@@ -16954,7 +17259,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="43">
         <v>98</v>
       </c>
@@ -17031,7 +17336,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="43">
         <v>99</v>
       </c>
@@ -17108,7 +17413,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="43">
         <v>100</v>
       </c>
@@ -17185,7 +17490,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="43">
         <v>101</v>
       </c>
@@ -17262,7 +17567,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="43">
         <v>102</v>
       </c>
@@ -17339,7 +17644,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="43">
         <v>103</v>
       </c>
@@ -17416,7 +17721,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="43">
         <v>104</v>
       </c>
@@ -17493,7 +17798,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="43">
         <v>105</v>
       </c>
@@ -17570,7 +17875,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="43">
         <v>106</v>
       </c>
@@ -17647,7 +17952,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="43">
         <v>107</v>
       </c>
@@ -17724,7 +18029,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="43">
         <v>108</v>
       </c>
@@ -17801,7 +18106,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="43">
         <v>109</v>
       </c>
@@ -17878,7 +18183,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="43">
         <v>110</v>
       </c>
@@ -17955,7 +18260,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="43">
         <v>111</v>
       </c>
@@ -18032,7 +18337,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="43">
         <v>112</v>
       </c>
@@ -18109,7 +18414,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="43">
         <v>113</v>
       </c>
@@ -18186,7 +18491,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="43">
         <v>114</v>
       </c>
@@ -18263,7 +18568,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="43">
         <v>115</v>
       </c>
@@ -18340,7 +18645,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="43">
         <v>116</v>
       </c>
@@ -18417,7 +18722,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="43">
         <v>117</v>
       </c>
@@ -18494,7 +18799,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="43">
         <v>118</v>
       </c>
@@ -18571,7 +18876,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="43">
         <v>119</v>
       </c>
@@ -18648,7 +18953,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="43">
         <v>120</v>
       </c>
@@ -18725,7 +19030,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="43">
         <v>121</v>
       </c>
@@ -18802,7 +19107,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="43">
         <v>122</v>
       </c>
@@ -18879,7 +19184,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="43">
         <v>123</v>
       </c>
@@ -18956,7 +19261,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="43">
         <v>124</v>
       </c>
@@ -19033,7 +19338,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="43">
         <v>125</v>
       </c>
@@ -19110,7 +19415,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="43">
         <v>126</v>
       </c>
@@ -19187,7 +19492,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="43">
         <v>127</v>
       </c>
@@ -19264,7 +19569,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="43">
         <v>128</v>
       </c>
@@ -19341,7 +19646,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="43">
         <v>129</v>
       </c>
@@ -19418,7 +19723,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="43">
         <v>130</v>
       </c>
@@ -19495,7 +19800,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="43">
         <v>131</v>
       </c>
@@ -19572,7 +19877,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="43">
         <v>132</v>
       </c>
@@ -19649,7 +19954,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="43">
         <v>133</v>
       </c>
@@ -19726,7 +20031,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="43">
         <v>134</v>
       </c>
@@ -19803,7 +20108,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="43">
         <v>135</v>
       </c>
@@ -19880,7 +20185,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="43">
         <v>136</v>
       </c>
@@ -19957,7 +20262,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="43">
         <v>137</v>
       </c>
@@ -20034,7 +20339,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="43">
         <v>138</v>
       </c>
@@ -20111,7 +20416,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="43">
         <v>139</v>
       </c>
@@ -20188,7 +20493,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="43">
         <v>140</v>
       </c>
@@ -20265,7 +20570,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="43">
         <v>141</v>
       </c>
@@ -20342,7 +20647,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="43">
         <v>142</v>
       </c>
@@ -20419,7 +20724,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="43">
         <v>143</v>
       </c>
@@ -20496,7 +20801,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="43">
         <v>144</v>
       </c>
@@ -20573,7 +20878,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="43">
         <v>145</v>
       </c>
@@ -20650,7 +20955,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="43">
         <v>146</v>
       </c>
@@ -20727,7 +21032,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="43">
         <v>147</v>
       </c>
@@ -20804,7 +21109,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="43">
         <v>148</v>
       </c>
@@ -20881,7 +21186,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="43">
         <v>149</v>
       </c>
@@ -20958,7 +21263,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="43">
         <v>150</v>
       </c>
@@ -21035,7 +21340,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="43">
         <v>151</v>
       </c>
@@ -21112,7 +21417,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="43">
         <v>152</v>
       </c>
@@ -21189,7 +21494,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="43">
         <v>153</v>
       </c>
@@ -21266,7 +21571,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="43">
         <v>154</v>
       </c>
@@ -21343,7 +21648,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="43">
         <v>155</v>
       </c>
@@ -21420,7 +21725,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="43">
         <v>156</v>
       </c>
@@ -21497,7 +21802,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="43">
         <v>157</v>
       </c>
@@ -21574,7 +21879,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="43">
         <v>158</v>
       </c>
@@ -21651,7 +21956,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="43">
         <v>159</v>
       </c>
@@ -21728,7 +22033,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="43">
         <v>160</v>
       </c>
@@ -21805,7 +22110,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="43">
         <v>161</v>
       </c>
@@ -21882,7 +22187,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="43">
         <v>162</v>
       </c>
@@ -21959,7 +22264,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="43">
         <v>163</v>
       </c>
@@ -22036,7 +22341,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="43">
         <v>164</v>
       </c>
@@ -22113,7 +22418,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="43">
         <v>165</v>
       </c>
@@ -22190,7 +22495,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="43">
         <v>166</v>
       </c>
@@ -22267,7 +22572,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="43">
         <v>167</v>
       </c>
@@ -22344,7 +22649,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="43">
         <v>168</v>
       </c>
@@ -22421,7 +22726,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="43">
         <v>169</v>
       </c>
@@ -22498,7 +22803,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="43">
         <v>170</v>
       </c>
@@ -22575,7 +22880,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="43">
         <v>171</v>
       </c>
@@ -22652,7 +22957,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="43">
         <v>172</v>
       </c>
@@ -22729,7 +23034,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="43">
         <v>173</v>
       </c>
@@ -22806,7 +23111,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="43">
         <v>174</v>
       </c>
@@ -22883,7 +23188,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="43">
         <v>175</v>
       </c>
@@ -22960,7 +23265,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="43">
         <v>176</v>
       </c>
@@ -23037,7 +23342,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="43">
         <v>177</v>
       </c>
@@ -23114,7 +23419,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="43">
         <v>178</v>
       </c>
@@ -23191,7 +23496,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="43">
         <v>179</v>
       </c>
@@ -23268,7 +23573,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="43">
         <v>180</v>
       </c>
@@ -23345,7 +23650,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="43">
         <v>181</v>
       </c>
@@ -23422,7 +23727,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="43">
         <v>182</v>
       </c>
@@ -23499,7 +23804,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="43">
         <v>183</v>
       </c>
@@ -23576,7 +23881,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="43">
         <v>184</v>
       </c>
@@ -23653,7 +23958,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="43">
         <v>185</v>
       </c>
@@ -23730,7 +24035,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="43">
         <v>186</v>
       </c>
@@ -23807,7 +24112,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="43">
         <v>187</v>
       </c>
@@ -23884,7 +24189,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="43">
         <v>188</v>
       </c>
@@ -23961,7 +24266,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="43">
         <v>189</v>
       </c>
@@ -24038,7 +24343,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="43">
         <v>190</v>
       </c>
@@ -24115,7 +24420,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="43">
         <v>191</v>
       </c>
@@ -24192,7 +24497,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="43">
         <v>192</v>
       </c>
@@ -24269,7 +24574,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="43">
         <v>193</v>
       </c>
@@ -24346,7 +24651,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="43">
         <v>194</v>
       </c>
@@ -24423,7 +24728,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="43">
         <v>195</v>
       </c>
@@ -24500,7 +24805,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="43">
         <v>196</v>
       </c>
@@ -24577,7 +24882,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="43">
         <v>197</v>
       </c>
@@ -24654,7 +24959,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="43">
         <v>198</v>
       </c>
@@ -24731,7 +25036,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="43">
         <v>199</v>
       </c>
@@ -24808,7 +25113,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="43">
         <v>200</v>
       </c>
@@ -24885,7 +25190,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="43">
         <v>201</v>
       </c>
@@ -24962,7 +25267,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="43">
         <v>202</v>
       </c>
@@ -25039,7 +25344,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="43">
         <v>203</v>
       </c>
@@ -25116,7 +25421,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="43">
         <v>204</v>
       </c>
@@ -25193,7 +25498,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="43">
         <v>205</v>
       </c>
@@ -25270,7 +25575,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="43">
         <v>206</v>
       </c>
@@ -25347,7 +25652,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="43">
         <v>207</v>
       </c>
@@ -25424,7 +25729,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="43">
         <v>208</v>
       </c>
@@ -25501,7 +25806,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="43">
         <v>209</v>
       </c>
@@ -25578,7 +25883,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="43">
         <v>210</v>
       </c>
@@ -25655,7 +25960,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="43">
         <v>211</v>
       </c>
@@ -25732,7 +26037,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="43">
         <v>212</v>
       </c>
@@ -25809,7 +26114,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="43">
         <v>213</v>
       </c>
@@ -25886,7 +26191,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="43">
         <v>214</v>
       </c>
@@ -25963,7 +26268,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="43">
         <v>215</v>
       </c>
@@ -26040,7 +26345,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="43">
         <v>216</v>
       </c>
@@ -26117,7 +26422,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="43">
         <v>217</v>
       </c>
@@ -26194,7 +26499,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="43">
         <v>218</v>
       </c>
@@ -26271,7 +26576,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="43">
         <v>219</v>
       </c>
@@ -26348,7 +26653,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="43">
         <v>220</v>
       </c>
@@ -26425,7 +26730,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="43">
         <v>221</v>
       </c>
@@ -26502,7 +26807,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="43">
         <v>222</v>
       </c>
@@ -26579,7 +26884,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="43">
         <v>223</v>
       </c>
@@ -26656,7 +26961,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="43">
         <v>224</v>
       </c>
@@ -26733,7 +27038,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="43">
         <v>225</v>
       </c>
@@ -26810,7 +27115,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="43">
         <v>226</v>
       </c>
@@ -26887,7 +27192,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="43">
         <v>227</v>
       </c>
@@ -26964,7 +27269,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="43">
         <v>228</v>
       </c>
@@ -27041,7 +27346,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="43">
         <v>229</v>
       </c>
@@ -27118,7 +27423,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="43">
         <v>230</v>
       </c>
@@ -27195,7 +27500,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="43">
         <v>231</v>
       </c>
@@ -27272,7 +27577,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="43">
         <v>232</v>
       </c>
@@ -27349,7 +27654,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="43">
         <v>233</v>
       </c>
@@ -27426,7 +27731,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="43">
         <v>234</v>
       </c>
@@ -27503,7 +27808,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="43">
         <v>235</v>
       </c>
@@ -27580,7 +27885,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="43">
         <v>236</v>
       </c>
@@ -27657,7 +27962,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="43">
         <v>237</v>
       </c>
@@ -27734,7 +28039,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="43">
         <v>238</v>
       </c>
@@ -27811,7 +28116,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="43">
         <v>239</v>
       </c>
@@ -27888,7 +28193,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="43">
         <v>240</v>
       </c>
@@ -27965,7 +28270,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="43">
         <v>241</v>
       </c>
@@ -28042,7 +28347,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="43">
         <v>242</v>
       </c>
@@ -28119,7 +28424,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="43">
         <v>243</v>
       </c>
@@ -28196,7 +28501,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="43">
         <v>244</v>
       </c>
@@ -28273,7 +28578,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="43">
         <v>245</v>
       </c>
@@ -28350,7 +28655,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="43">
         <v>246</v>
       </c>
@@ -28427,7 +28732,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="43">
         <v>247</v>
       </c>
@@ -28504,7 +28809,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="43">
         <v>248</v>
       </c>
@@ -28581,7 +28886,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="43">
         <v>249</v>
       </c>
@@ -28658,7 +28963,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="43">
         <v>250</v>
       </c>
@@ -28735,7 +29040,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="43">
         <v>251</v>
       </c>
@@ -28812,7 +29117,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="43">
         <v>252</v>
       </c>
@@ -28889,7 +29194,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="43">
         <v>253</v>
       </c>
@@ -28966,7 +29271,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="43">
         <v>254</v>
       </c>
@@ -29043,7 +29348,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="43">
         <v>255</v>
       </c>
@@ -29120,7 +29425,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="43">
         <v>256</v>
       </c>
@@ -29197,7 +29502,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="43">
         <v>257</v>
       </c>
@@ -29274,7 +29579,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="43">
         <v>258</v>
       </c>
@@ -29351,7 +29656,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="43">
         <v>259</v>
       </c>
@@ -29428,7 +29733,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="43">
         <v>260</v>
       </c>
@@ -29505,7 +29810,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="43">
         <v>261</v>
       </c>
@@ -29582,7 +29887,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="43">
         <v>262</v>
       </c>
@@ -29659,7 +29964,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="43">
         <v>263</v>
       </c>
@@ -29736,7 +30041,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="43">
         <v>264</v>
       </c>
@@ -29813,7 +30118,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="43">
         <v>265</v>
       </c>
@@ -29890,7 +30195,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="43">
         <v>266</v>
       </c>
@@ -29967,7 +30272,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="43">
         <v>267</v>
       </c>
@@ -30044,7 +30349,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="43">
         <v>268</v>
       </c>
@@ -30121,7 +30426,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="43">
         <v>269</v>
       </c>
@@ -30198,7 +30503,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="43">
         <v>270</v>
       </c>
@@ -30275,7 +30580,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="43">
         <v>271</v>
       </c>
@@ -30352,7 +30657,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="43">
         <v>272</v>
       </c>
@@ -30429,7 +30734,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="43">
         <v>273</v>
       </c>
@@ -30506,7 +30811,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="43">
         <v>274</v>
       </c>
@@ -30583,7 +30888,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="43">
         <v>275</v>
       </c>
@@ -30660,7 +30965,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="43">
         <v>276</v>
       </c>
@@ -30737,7 +31042,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="43">
         <v>277</v>
       </c>
@@ -30814,7 +31119,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="43">
         <v>278</v>
       </c>
@@ -30891,7 +31196,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="43">
         <v>279</v>
       </c>
@@ -30968,7 +31273,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="43">
         <v>280</v>
       </c>
@@ -31045,7 +31350,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="43">
         <v>281</v>
       </c>
@@ -31122,7 +31427,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="43">
         <v>282</v>
       </c>
@@ -31199,7 +31504,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="43">
         <v>283</v>
       </c>
@@ -31276,7 +31581,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="43">
         <v>284</v>
       </c>
@@ -31353,7 +31658,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="43">
         <v>285</v>
       </c>
@@ -31430,7 +31735,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="43">
         <v>286</v>
       </c>
@@ -31507,7 +31812,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="43">
         <v>287</v>
       </c>
@@ -31584,7 +31889,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="43">
         <v>288</v>
       </c>
@@ -31661,7 +31966,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="43">
         <v>289</v>
       </c>
@@ -31738,7 +32043,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="43">
         <v>290</v>
       </c>
@@ -31815,7 +32120,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="43">
         <v>291</v>
       </c>
@@ -31892,7 +32197,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="43">
         <v>292</v>
       </c>
@@ -31969,7 +32274,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="43">
         <v>293</v>
       </c>
@@ -32046,7 +32351,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="43">
         <v>294</v>
       </c>
@@ -32123,7 +32428,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="43">
         <v>295</v>
       </c>
@@ -32200,7 +32505,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="43">
         <v>296</v>
       </c>
@@ -32277,7 +32582,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="43">
         <v>297</v>
       </c>
@@ -32354,7 +32659,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="43">
         <v>298</v>
       </c>
@@ -32431,7 +32736,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="43">
         <v>299</v>
       </c>
@@ -32508,7 +32813,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="43">
         <v>300</v>
       </c>
@@ -32585,7 +32890,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="43">
         <v>301</v>
       </c>
@@ -32662,7 +32967,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="43">
         <v>302</v>
       </c>
@@ -32739,7 +33044,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="43">
         <v>303</v>
       </c>
@@ -32816,7 +33121,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="43">
         <v>304</v>
       </c>
@@ -32893,7 +33198,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="43">
         <v>305</v>
       </c>
@@ -32970,7 +33275,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="43">
         <v>306</v>
       </c>
@@ -33047,7 +33352,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="43">
         <v>307</v>
       </c>
@@ -33124,7 +33429,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="43">
         <v>308</v>
       </c>
@@ -33201,7 +33506,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="43">
         <v>309</v>
       </c>
@@ -33278,7 +33583,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="43">
         <v>310</v>
       </c>
@@ -33355,7 +33660,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="43">
         <v>311</v>
       </c>
@@ -33432,7 +33737,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="43">
         <v>312</v>
       </c>
@@ -33509,7 +33814,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="43">
         <v>313</v>
       </c>
@@ -33586,7 +33891,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="43">
         <v>314</v>
       </c>
@@ -33663,7 +33968,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="43">
         <v>315</v>
       </c>
@@ -33740,7 +34045,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="43">
         <v>316</v>
       </c>
@@ -33817,7 +34122,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="43">
         <v>317</v>
       </c>
@@ -33894,7 +34199,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="43">
         <v>318</v>
       </c>
@@ -33971,7 +34276,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="43">
         <v>319</v>
       </c>
@@ -34048,7 +34353,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="43">
         <v>320</v>
       </c>
@@ -34125,7 +34430,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="43">
         <v>321</v>
       </c>
@@ -34202,7 +34507,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="43">
         <v>322</v>
       </c>
@@ -34279,7 +34584,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="43">
         <v>323</v>
       </c>
@@ -34356,7 +34661,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="43">
         <v>324</v>
       </c>
@@ -34433,7 +34738,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="43">
         <v>325</v>
       </c>
@@ -34510,7 +34815,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="43">
         <v>326</v>
       </c>
@@ -34587,7 +34892,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="43">
         <v>327</v>
       </c>
@@ -34664,7 +34969,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="43">
         <v>328</v>
       </c>
@@ -34741,7 +35046,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="43">
         <v>329</v>
       </c>
@@ -34818,7 +35123,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="43">
         <v>330</v>
       </c>
@@ -34895,7 +35200,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="43">
         <v>331</v>
       </c>
@@ -34972,7 +35277,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="43">
         <v>332</v>
       </c>
@@ -35049,7 +35354,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="43">
         <v>333</v>
       </c>
@@ -35126,7 +35431,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="43">
         <v>334</v>
       </c>
@@ -35203,7 +35508,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="43">
         <v>335</v>
       </c>
@@ -35280,7 +35585,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="43">
         <v>336</v>
       </c>
@@ -35357,7 +35662,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="43">
         <v>337</v>
       </c>
@@ -35434,7 +35739,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="43">
         <v>338</v>
       </c>
@@ -35511,7 +35816,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="43">
         <v>339</v>
       </c>
@@ -35588,7 +35893,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="43">
         <v>340</v>
       </c>
@@ -35665,7 +35970,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="43">
         <v>341</v>
       </c>
@@ -35742,7 +36047,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="43">
         <v>342</v>
       </c>
@@ -35819,7 +36124,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="43">
         <v>343</v>
       </c>
@@ -35896,7 +36201,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="43">
         <v>344</v>
       </c>
@@ -35973,7 +36278,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="43">
         <v>345</v>
       </c>
@@ -36050,7 +36355,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="43">
         <v>346</v>
       </c>
@@ -36127,7 +36432,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="43">
         <v>347</v>
       </c>
@@ -36204,7 +36509,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="43">
         <v>348</v>
       </c>
@@ -36281,7 +36586,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="43">
         <v>349</v>
       </c>
@@ -36358,7 +36663,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="43">
         <v>350</v>
       </c>
@@ -36435,7 +36740,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="43">
         <v>351</v>
       </c>
@@ -36512,7 +36817,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="43">
         <v>352</v>
       </c>
@@ -36589,7 +36894,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="43">
         <v>353</v>
       </c>
@@ -36666,7 +36971,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="43">
         <v>354</v>
       </c>
@@ -36743,7 +37048,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="43">
         <v>355</v>
       </c>
@@ -36820,7 +37125,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="43">
         <v>356</v>
       </c>
@@ -36897,7 +37202,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="43">
         <v>357</v>
       </c>
@@ -36974,7 +37279,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="43">
         <v>358</v>
       </c>
@@ -37051,7 +37356,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="43">
         <v>359</v>
       </c>
@@ -37128,7 +37433,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="43">
         <v>360</v>
       </c>
@@ -37205,7 +37510,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="43">
         <v>361</v>
       </c>
@@ -37282,7 +37587,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="43">
         <v>362</v>
       </c>
@@ -37359,7 +37664,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="43">
         <v>363</v>
       </c>
@@ -37436,7 +37741,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="43">
         <v>364</v>
       </c>
@@ -37513,7 +37818,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="43">
         <v>365</v>
       </c>
@@ -37590,7 +37895,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="43">
         <v>366</v>
       </c>
@@ -37667,7 +37972,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="43">
         <v>367</v>
       </c>
@@ -37744,7 +38049,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="43">
         <v>368</v>
       </c>
@@ -37821,7 +38126,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="43">
         <v>369</v>
       </c>
@@ -37898,7 +38203,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="43">
         <v>370</v>
       </c>
@@ -37975,7 +38280,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="43">
         <v>371</v>
       </c>
@@ -38052,7 +38357,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="43">
         <v>372</v>
       </c>
@@ -38129,7 +38434,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="43">
         <v>373</v>
       </c>
@@ -38206,7 +38511,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="43">
         <v>374</v>
       </c>
@@ -38283,7 +38588,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="375" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="43">
         <v>375</v>
       </c>
@@ -38360,7 +38665,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="376" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="43">
         <v>376</v>
       </c>
@@ -38437,7 +38742,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="377" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="43">
         <v>377</v>
       </c>
@@ -38514,7 +38819,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="378" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="43">
         <v>378</v>
       </c>
@@ -38591,7 +38896,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="379" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="43">
         <v>379</v>
       </c>
@@ -38668,7 +38973,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="380" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="43">
         <v>380</v>
       </c>
@@ -38745,7 +39050,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="381" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="43">
         <v>381</v>
       </c>
@@ -38822,7 +39127,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="382" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="43">
         <v>382</v>
       </c>
@@ -38899,7 +39204,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="383" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="43">
         <v>383</v>
       </c>
@@ -38976,7 +39281,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="384" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="43">
         <v>384</v>
       </c>
@@ -39053,7 +39358,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="385" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="43">
         <v>385</v>
       </c>
@@ -39130,7 +39435,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="386" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="43">
         <v>386</v>
       </c>
@@ -39207,7 +39512,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="387" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="43">
         <v>387</v>
       </c>
@@ -39284,7 +39589,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="388" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="43">
         <v>388</v>
       </c>
@@ -39361,7 +39666,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="389" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="43">
         <v>389</v>
       </c>
@@ -39438,7 +39743,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="390" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="43">
         <v>390</v>
       </c>
@@ -39515,7 +39820,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="391" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="43">
         <v>391</v>
       </c>
@@ -39592,7 +39897,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="392" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="43">
         <v>392</v>
       </c>
@@ -39669,7 +39974,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="393" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="43">
         <v>393</v>
       </c>
@@ -39746,7 +40051,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="394" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="43">
         <v>394</v>
       </c>
@@ -39823,7 +40128,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="395" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="43">
         <v>395</v>
       </c>
@@ -39900,7 +40205,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="396" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="43">
         <v>396</v>
       </c>
@@ -39977,7 +40282,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="397" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="43">
         <v>397</v>
       </c>
@@ -40054,7 +40359,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="398" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="43">
         <v>398</v>
       </c>
@@ -40131,7 +40436,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="399" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="43">
         <v>399</v>
       </c>
@@ -40208,7 +40513,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="400" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="43">
         <v>400</v>
       </c>
@@ -40285,7 +40590,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="401" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="43">
         <v>401</v>
       </c>
@@ -40362,7 +40667,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="402" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="43">
         <v>402</v>
       </c>
@@ -40439,7 +40744,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="403" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="43">
         <v>403</v>
       </c>
@@ -40516,7 +40821,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="404" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="43">
         <v>404</v>
       </c>
@@ -40593,7 +40898,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="405" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="43">
         <v>405</v>
       </c>
@@ -40670,7 +40975,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="406" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="43">
         <v>406</v>
       </c>
@@ -40747,7 +41052,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="407" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="43">
         <v>407</v>
       </c>
@@ -40824,7 +41129,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="408" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="43">
         <v>408</v>
       </c>
@@ -40901,7 +41206,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="409" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="43">
         <v>409</v>
       </c>
@@ -40978,7 +41283,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="410" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="43">
         <v>410</v>
       </c>
@@ -41055,7 +41360,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="411" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="43">
         <v>411</v>
       </c>
@@ -41132,7 +41437,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="412" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="43">
         <v>412</v>
       </c>
@@ -41209,7 +41514,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="413" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="43">
         <v>413</v>
       </c>
@@ -41286,7 +41591,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="414" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="43">
         <v>414</v>
       </c>
@@ -41363,7 +41668,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="415" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="43">
         <v>415</v>
       </c>
@@ -41440,7 +41745,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="416" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="43">
         <v>416</v>
       </c>
@@ -41517,7 +41822,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="417" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="43">
         <v>417</v>
       </c>
@@ -41594,7 +41899,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="418" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="43">
         <v>418</v>
       </c>
@@ -41671,7 +41976,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="419" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="43">
         <v>419</v>
       </c>
@@ -41748,7 +42053,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="420" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="43">
         <v>420</v>
       </c>
@@ -41825,7 +42130,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="421" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="43">
         <v>421</v>
       </c>
@@ -41902,7 +42207,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="422" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="43">
         <v>422</v>
       </c>
@@ -41979,7 +42284,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="423" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="43">
         <v>423</v>
       </c>
@@ -42056,7 +42361,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="424" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="43">
         <v>424</v>
       </c>
@@ -42133,7 +42438,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="425" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="43">
         <v>425</v>
       </c>
@@ -42210,7 +42515,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="426" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="43">
         <v>426</v>
       </c>
@@ -42287,7 +42592,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="427" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="43">
         <v>427</v>
       </c>
@@ -42364,7 +42669,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="428" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="43">
         <v>428</v>
       </c>
@@ -42441,7 +42746,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="429" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="43">
         <v>429</v>
       </c>
@@ -42518,7 +42823,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="430" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="43">
         <v>430</v>
       </c>
@@ -42595,7 +42900,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="431" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="43">
         <v>431</v>
       </c>
@@ -42672,7 +42977,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="432" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="43">
         <v>432</v>
       </c>
@@ -42749,7 +43054,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="433" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="43">
         <v>433</v>
       </c>
@@ -42826,7 +43131,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="434" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="43">
         <v>434</v>
       </c>
@@ -42903,7 +43208,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="435" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="43">
         <v>435</v>
       </c>
@@ -42980,7 +43285,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="436" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="43">
         <v>436</v>
       </c>
@@ -43057,7 +43362,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="437" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="43">
         <v>437</v>
       </c>
@@ -43134,7 +43439,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="438" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="43">
         <v>438</v>
       </c>
@@ -43211,7 +43516,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="439" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="43">
         <v>439</v>
       </c>
@@ -43288,7 +43593,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="440" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="43">
         <v>440</v>
       </c>
@@ -43365,7 +43670,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="441" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="43">
         <v>441</v>
       </c>
@@ -43442,7 +43747,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="442" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="43">
         <v>442</v>
       </c>
@@ -43519,7 +43824,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="443" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="43">
         <v>443</v>
       </c>
@@ -43596,7 +43901,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="444" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="43">
         <v>444</v>
       </c>
@@ -43673,7 +43978,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="445" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="43">
         <v>445</v>
       </c>
@@ -43750,7 +44055,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="446" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="43">
         <v>446</v>
       </c>
@@ -43827,7 +44132,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="447" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="43">
         <v>447</v>
       </c>
@@ -43904,7 +44209,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="448" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="43">
         <v>448</v>
       </c>
@@ -43981,7 +44286,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="449" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="43">
         <v>449</v>
       </c>
@@ -44058,7 +44363,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="450" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="43">
         <v>450</v>
       </c>
@@ -44135,7 +44440,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="451" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="43">
         <v>451</v>
       </c>
@@ -44212,7 +44517,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="452" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="43">
         <v>452</v>
       </c>
@@ -44289,7 +44594,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="453" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="43">
         <v>453</v>
       </c>
@@ -44366,7 +44671,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="454" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="43">
         <v>454</v>
       </c>
@@ -44443,7 +44748,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="455" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="43">
         <v>455</v>
       </c>
@@ -44520,7 +44825,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="456" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="43">
         <v>456</v>
       </c>
@@ -44597,7 +44902,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="457" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="43">
         <v>457</v>
       </c>
@@ -44674,7 +44979,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="458" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="43">
         <v>458</v>
       </c>
@@ -44751,7 +45056,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="459" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="43">
         <v>459</v>
       </c>
@@ -44828,7 +45133,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="460" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="43">
         <v>460</v>
       </c>
@@ -44905,7 +45210,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="461" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="43">
         <v>461</v>
       </c>
@@ -44982,7 +45287,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="462" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="43">
         <v>462</v>
       </c>
@@ -45059,7 +45364,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="463" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="43">
         <v>463</v>
       </c>
@@ -45136,7 +45441,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="464" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="43">
         <v>464</v>
       </c>
@@ -45213,7 +45518,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="465" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="43">
         <v>465</v>
       </c>
@@ -45290,7 +45595,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="466" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="43">
         <v>466</v>
       </c>
@@ -45367,7 +45672,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="467" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="43">
         <v>467</v>
       </c>
@@ -45444,7 +45749,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="468" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="43">
         <v>468</v>
       </c>
@@ -45521,7 +45826,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="469" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="43">
         <v>469</v>
       </c>
@@ -45598,7 +45903,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="470" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="43">
         <v>470</v>
       </c>
@@ -45675,7 +45980,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="471" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="43">
         <v>471</v>
       </c>
@@ -45752,7 +46057,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="472" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="43">
         <v>472</v>
       </c>
@@ -45829,7 +46134,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="473" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="43">
         <v>473</v>
       </c>
@@ -45906,7 +46211,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="474" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="43">
         <v>474</v>
       </c>
@@ -45983,7 +46288,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="475" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="43">
         <v>475</v>
       </c>
@@ -46060,7 +46365,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="476" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="43">
         <v>476</v>
       </c>
@@ -46137,7 +46442,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="477" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="43">
         <v>477</v>
       </c>
@@ -46214,7 +46519,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="478" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="43">
         <v>478</v>
       </c>
@@ -46291,7 +46596,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="479" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="43">
         <v>479</v>
       </c>
@@ -46368,7 +46673,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="480" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="43">
         <v>480</v>
       </c>
@@ -46445,7 +46750,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="481" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="43">
         <v>481</v>
       </c>
@@ -46522,7 +46827,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="482" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="43">
         <v>482</v>
       </c>
@@ -46599,7 +46904,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="483" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="43">
         <v>483</v>
       </c>
@@ -46676,7 +46981,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="484" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="43">
         <v>484</v>
       </c>
@@ -46753,7 +47058,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="485" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="43">
         <v>485</v>
       </c>
@@ -46830,7 +47135,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="486" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="43">
         <v>486</v>
       </c>
@@ -46907,7 +47212,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="487" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="43">
         <v>487</v>
       </c>
@@ -46984,7 +47289,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="488" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="43">
         <v>488</v>
       </c>
@@ -47061,7 +47366,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="489" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="43">
         <v>489</v>
       </c>
@@ -47138,7 +47443,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="490" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="43">
         <v>490</v>
       </c>
@@ -47215,7 +47520,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="491" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="43">
         <v>491</v>
       </c>
@@ -47292,7 +47597,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="492" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="43">
         <v>492</v>
       </c>
@@ -47369,7 +47674,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="493" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="43">
         <v>493</v>
       </c>
@@ -47446,7 +47751,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="494" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="43">
         <v>494</v>
       </c>
@@ -47523,7 +47828,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="495" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="43">
         <v>495</v>
       </c>
@@ -47600,7 +47905,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="496" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="43">
         <v>496</v>
       </c>
@@ -47677,7 +47982,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="497" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="43">
         <v>497</v>
       </c>
@@ -47754,7 +48059,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="498" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="43">
         <v>498</v>
       </c>
@@ -47831,7 +48136,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="499" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="43">
         <v>499</v>
       </c>
@@ -47908,7 +48213,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="43">
         <v>500</v>
       </c>
@@ -47985,7 +48290,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="501" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="43">
         <v>501</v>
       </c>
@@ -48062,7 +48367,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="502" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="43">
         <v>502</v>
       </c>
@@ -48139,7 +48444,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="503" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="43">
         <v>503</v>
       </c>
@@ -48216,7 +48521,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="504" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="43">
         <v>504</v>
       </c>
@@ -48293,7 +48598,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="505" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="43">
         <v>505</v>
       </c>
@@ -48370,7 +48675,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="506" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="43">
         <v>506</v>
       </c>
@@ -48447,7 +48752,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="507" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="43">
         <v>507</v>
       </c>
@@ -48524,7 +48829,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="508" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="43">
         <v>508</v>
       </c>
@@ -48601,7 +48906,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="509" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="43">
         <v>509</v>
       </c>
@@ -48678,7 +48983,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="510" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="43">
         <v>510</v>
       </c>
@@ -48755,7 +49060,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="511" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="43">
         <v>511</v>
       </c>
@@ -48832,7 +49137,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="512" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="43">
         <v>512</v>
       </c>
@@ -48909,7 +49214,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="513" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="43">
         <v>513</v>
       </c>
@@ -48986,7 +49291,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="514" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="43">
         <v>514</v>
       </c>
@@ -49063,7 +49368,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="515" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="43">
         <v>515</v>
       </c>
@@ -49140,7 +49445,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="516" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="43">
         <v>516</v>
       </c>
@@ -49217,7 +49522,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="517" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="43">
         <v>517</v>
       </c>
@@ -49294,7 +49599,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="518" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="43">
         <v>518</v>
       </c>
@@ -49371,7 +49676,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="519" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="43">
         <v>519</v>
       </c>
@@ -49448,7 +49753,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="520" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="43">
         <v>520</v>
       </c>
@@ -49525,7 +49830,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="521" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="43">
         <v>521</v>
       </c>
@@ -49602,7 +49907,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="522" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="43">
         <v>522</v>
       </c>
@@ -49679,7 +49984,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="523" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="43">
         <v>523</v>
       </c>
@@ -49756,7 +50061,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="524" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="43">
         <v>524</v>
       </c>
@@ -49833,7 +50138,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="525" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="43">
         <v>525</v>
       </c>
@@ -49910,7 +50215,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="526" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="43">
         <v>526</v>
       </c>
@@ -49987,7 +50292,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="527" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="43">
         <v>527</v>
       </c>
@@ -50064,7 +50369,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="528" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="43">
         <v>528</v>
       </c>
@@ -50141,7 +50446,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="529" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="43">
         <v>529</v>
       </c>
@@ -50218,7 +50523,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="530" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="43">
         <v>530</v>
       </c>
@@ -50295,7 +50600,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="531" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="43">
         <v>531</v>
       </c>
@@ -50372,7 +50677,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="532" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="43">
         <v>532</v>
       </c>
@@ -50449,7 +50754,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="533" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="43">
         <v>533</v>
       </c>
@@ -50526,7 +50831,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="534" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="43">
         <v>534</v>
       </c>
@@ -50603,7 +50908,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="535" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="43">
         <v>535</v>
       </c>
@@ -50680,7 +50985,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="536" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="43">
         <v>536</v>
       </c>
@@ -50757,7 +51062,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="537" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="43">
         <v>537</v>
       </c>
@@ -50834,7 +51139,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="538" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="43">
         <v>538</v>
       </c>
@@ -50911,7 +51216,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="539" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="43">
         <v>539</v>
       </c>
@@ -50988,7 +51293,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="540" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="43">
         <v>540</v>
       </c>
@@ -51065,7 +51370,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="541" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="43">
         <v>541</v>
       </c>
@@ -51142,7 +51447,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="542" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="43">
         <v>542</v>
       </c>
@@ -51219,7 +51524,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="543" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="43">
         <v>543</v>
       </c>
@@ -51296,7 +51601,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="544" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="43">
         <v>544</v>
       </c>
@@ -51373,7 +51678,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="545" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="43">
         <v>545</v>
       </c>
@@ -51450,7 +51755,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="546" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="43">
         <v>546</v>
       </c>
@@ -51527,7 +51832,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="547" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="43">
         <v>547</v>
       </c>
@@ -51604,7 +51909,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="548" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="43">
         <v>548</v>
       </c>
@@ -51681,7 +51986,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="549" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="43">
         <v>549</v>
       </c>
@@ -51758,7 +52063,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="550" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="43">
         <v>550</v>
       </c>
@@ -51835,7 +52140,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="551" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="43">
         <v>551</v>
       </c>
@@ -51912,7 +52217,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="552" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="43">
         <v>552</v>
       </c>
@@ -51989,7 +52294,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="553" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="43">
         <v>553</v>
       </c>
@@ -52066,7 +52371,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="554" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="43">
         <v>554</v>
       </c>
@@ -52143,7 +52448,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="555" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="43">
         <v>555</v>
       </c>
@@ -52220,7 +52525,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="556" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="43">
         <v>556</v>
       </c>
@@ -52297,7 +52602,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="557" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="43">
         <v>557</v>
       </c>
@@ -52374,7 +52679,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="558" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="43">
         <v>558</v>
       </c>
@@ -52451,7 +52756,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="559" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="43">
         <v>559</v>
       </c>
@@ -52528,7 +52833,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="560" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="43">
         <v>560</v>
       </c>
@@ -52605,7 +52910,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="561" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="43">
         <v>561</v>
       </c>
@@ -52682,7 +52987,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="562" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="43">
         <v>562</v>
       </c>
@@ -52759,7 +53064,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="563" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="43">
         <v>563</v>
       </c>
@@ -52836,7 +53141,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="564" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="43">
         <v>564</v>
       </c>
@@ -52913,7 +53218,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="565" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="43">
         <v>565</v>
       </c>
@@ -52990,7 +53295,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="566" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="43">
         <v>566</v>
       </c>
@@ -53067,7 +53372,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="567" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="43">
         <v>567</v>
       </c>
@@ -53144,7 +53449,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="568" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="43">
         <v>568</v>
       </c>
@@ -53221,7 +53526,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="569" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="43">
         <v>569</v>
       </c>
@@ -53298,7 +53603,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="570" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="43">
         <v>570</v>
       </c>
@@ -53375,7 +53680,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="571" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="43">
         <v>571</v>
       </c>
@@ -53452,7 +53757,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="572" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="43">
         <v>572</v>
       </c>
@@ -53529,7 +53834,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="573" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="43">
         <v>573</v>
       </c>
@@ -53606,7 +53911,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="574" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="43">
         <v>574</v>
       </c>
@@ -53683,7 +53988,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="575" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="43">
         <v>575</v>
       </c>
@@ -53760,7 +54065,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="576" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="43">
         <v>576</v>
       </c>
@@ -53837,7 +54142,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="577" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="43">
         <v>577</v>
       </c>
@@ -53914,7 +54219,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="578" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="43">
         <v>578</v>
       </c>
@@ -53991,7 +54296,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="579" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="43">
         <v>579</v>
       </c>
@@ -54068,7 +54373,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="580" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="43">
         <v>580</v>
       </c>
@@ -54145,7 +54450,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="581" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="43">
         <v>581</v>
       </c>
@@ -54222,7 +54527,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="582" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="43">
         <v>582</v>
       </c>
@@ -54299,7 +54604,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="583" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="43">
         <v>583</v>
       </c>
@@ -54376,7 +54681,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="584" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="43">
         <v>584</v>
       </c>
@@ -54453,7 +54758,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="585" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="43">
         <v>585</v>
       </c>
@@ -54530,7 +54835,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="586" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="43">
         <v>586</v>
       </c>
@@ -54607,7 +54912,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="587" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="43">
         <v>587</v>
       </c>
@@ -54684,7 +54989,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="588" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="43">
         <v>588</v>
       </c>
@@ -54761,7 +55066,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="589" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="43">
         <v>589</v>
       </c>
@@ -54838,7 +55143,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="590" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="43">
         <v>590</v>
       </c>
@@ -54915,7 +55220,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="591" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="43">
         <v>591</v>
       </c>
@@ -54992,7 +55297,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="592" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="43">
         <v>592</v>
       </c>
@@ -55069,7 +55374,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="593" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="43">
         <v>593</v>
       </c>
@@ -55146,7 +55451,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="594" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="43">
         <v>594</v>
       </c>
@@ -55223,7 +55528,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="595" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="43">
         <v>595</v>
       </c>
@@ -55300,7 +55605,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="596" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="43">
         <v>596</v>
       </c>
@@ -55377,7 +55682,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="597" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="43">
         <v>597</v>
       </c>
@@ -55454,7 +55759,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="598" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="43">
         <v>598</v>
       </c>
@@ -55531,7 +55836,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="599" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="43">
         <v>599</v>
       </c>
@@ -55608,7 +55913,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="600" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="43">
         <v>600</v>
       </c>
@@ -55685,7 +55990,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="601" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="43">
         <v>601</v>
       </c>
@@ -55762,7 +56067,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="602" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="43">
         <v>602</v>
       </c>
@@ -55839,7 +56144,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="603" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="43">
         <v>603</v>
       </c>
@@ -55916,7 +56221,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="604" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="43">
         <v>604</v>
       </c>
@@ -55993,7 +56298,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="605" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="43">
         <v>605</v>
       </c>
@@ -56070,7 +56375,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="606" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="43">
         <v>606</v>
       </c>
@@ -56147,7 +56452,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="607" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="43">
         <v>607</v>
       </c>
@@ -56224,7 +56529,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="608" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="43">
         <v>608</v>
       </c>
@@ -56301,7 +56606,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="609" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="43">
         <v>609</v>
       </c>
@@ -56378,7 +56683,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="610" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="43">
         <v>610</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_2Q.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252B083E-61B0-401E-9B2E-764FDCC54618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE48989-E3D3-4E8D-BE28-16FB6C950BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20622" uniqueCount="1607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20661" uniqueCount="1608">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4912,6 +4912,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -5561,14 +5564,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color theme="0"/>
       </font>
     </dxf>
@@ -5710,6 +5705,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6250,7 +6253,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.462103124999</v>
+        <v>46268.68605462963</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>1307</v>
@@ -6504,7 +6507,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
@@ -6512,7 +6515,7 @@
     <col min="3" max="3" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="33" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" style="33" customWidth="1"/>
     <col min="7" max="11" width="11.83203125" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
@@ -6532,9 +6535,10 @@
     <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="8" style="33" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>1251</v>
       </c>
@@ -6622,8 +6626,11 @@
       <c r="AC1" s="11" t="s">
         <v>1274</v>
       </c>
+      <c r="AD1" s="11" t="s">
+        <v>1607</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="54">
         <v>2</v>
       </c>
@@ -6719,8 +6726,11 @@
       <c r="AC2" s="37" t="s">
         <v>1329</v>
       </c>
+      <c r="AD2" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="54">
         <v>3</v>
       </c>
@@ -6816,8 +6826,11 @@
       <c r="AC3" s="37" t="s">
         <v>1330</v>
       </c>
+      <c r="AD3" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="54">
         <v>4</v>
       </c>
@@ -6913,8 +6926,11 @@
       <c r="AC4" s="37" t="s">
         <v>1331</v>
       </c>
+      <c r="AD4" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="54">
         <v>5</v>
       </c>
@@ -7010,8 +7026,11 @@
       <c r="AC5" s="37" t="s">
         <v>1332</v>
       </c>
+      <c r="AD5" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="54">
         <v>6</v>
       </c>
@@ -7107,8 +7126,11 @@
       <c r="AC6" s="37" t="s">
         <v>1333</v>
       </c>
+      <c r="AD6" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="54">
         <v>7</v>
       </c>
@@ -7204,8 +7226,11 @@
       <c r="AC7" s="37" t="s">
         <v>1334</v>
       </c>
+      <c r="AD7" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="54">
         <v>8</v>
       </c>
@@ -7301,8 +7326,11 @@
       <c r="AC8" s="37" t="s">
         <v>1335</v>
       </c>
+      <c r="AD8" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="54">
         <v>9</v>
       </c>
@@ -7398,8 +7426,11 @@
       <c r="AC9" s="37" t="s">
         <v>1243</v>
       </c>
+      <c r="AD9" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="54">
         <v>10</v>
       </c>
@@ -7495,8 +7526,11 @@
       <c r="AC10" s="37" t="s">
         <v>1336</v>
       </c>
+      <c r="AD10" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="54">
         <v>11</v>
       </c>
@@ -7592,8 +7626,11 @@
       <c r="AC11" s="37" t="s">
         <v>1337</v>
       </c>
+      <c r="AD11" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="54">
         <v>12</v>
       </c>
@@ -7689,8 +7726,11 @@
       <c r="AC12" s="37" t="s">
         <v>1338</v>
       </c>
+      <c r="AD12" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="54">
         <v>13</v>
       </c>
@@ -7786,8 +7826,11 @@
       <c r="AC13" s="37" t="s">
         <v>1339</v>
       </c>
+      <c r="AD13" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="54">
         <v>14</v>
       </c>
@@ -7883,8 +7926,11 @@
       <c r="AC14" s="37" t="s">
         <v>1340</v>
       </c>
+      <c r="AD14" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="54">
         <v>15</v>
       </c>
@@ -7980,8 +8026,11 @@
       <c r="AC15" s="74" t="s">
         <v>1362</v>
       </c>
+      <c r="AD15" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="54">
         <v>16</v>
       </c>
@@ -8077,8 +8126,11 @@
       <c r="AC16" s="74" t="s">
         <v>1437</v>
       </c>
+      <c r="AD16" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="54">
         <v>17</v>
       </c>
@@ -8174,8 +8226,11 @@
       <c r="AC17" s="74" t="s">
         <v>1363</v>
       </c>
+      <c r="AD17" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="54">
         <v>18</v>
       </c>
@@ -8271,8 +8326,11 @@
       <c r="AC18" s="74" t="s">
         <v>1364</v>
       </c>
+      <c r="AD18" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="54">
         <v>19</v>
       </c>
@@ -8368,8 +8426,11 @@
       <c r="AC19" s="74" t="s">
         <v>1365</v>
       </c>
+      <c r="AD19" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="54">
         <v>20</v>
       </c>
@@ -8465,8 +8526,11 @@
       <c r="AC20" s="74" t="s">
         <v>1366</v>
       </c>
+      <c r="AD20" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="54">
         <v>21</v>
       </c>
@@ -8562,8 +8626,11 @@
       <c r="AC21" s="74" t="s">
         <v>1367</v>
       </c>
+      <c r="AD21" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="54">
         <v>22</v>
       </c>
@@ -8659,8 +8726,11 @@
       <c r="AC22" s="74" t="s">
         <v>1407</v>
       </c>
+      <c r="AD22" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="54">
         <v>23</v>
       </c>
@@ -8756,8 +8826,11 @@
       <c r="AC23" s="74" t="s">
         <v>1408</v>
       </c>
+      <c r="AD23" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="54">
         <v>24</v>
       </c>
@@ -8853,8 +8926,11 @@
       <c r="AC24" s="74" t="s">
         <v>1409</v>
       </c>
+      <c r="AD24" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="54">
         <v>25</v>
       </c>
@@ -8950,8 +9026,11 @@
       <c r="AC25" s="74" t="s">
         <v>1410</v>
       </c>
+      <c r="AD25" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="54">
         <v>26</v>
       </c>
@@ -9047,8 +9126,11 @@
       <c r="AC26" s="74" t="s">
         <v>1411</v>
       </c>
+      <c r="AD26" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="54">
         <v>27</v>
       </c>
@@ -9144,8 +9226,11 @@
       <c r="AC27" s="74" t="s">
         <v>1412</v>
       </c>
+      <c r="AD27" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="54">
         <v>28</v>
       </c>
@@ -9241,8 +9326,11 @@
       <c r="AC28" s="74" t="s">
         <v>1413</v>
       </c>
+      <c r="AD28" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="54">
         <v>29</v>
       </c>
@@ -9338,8 +9426,11 @@
       <c r="AC29" s="74" t="s">
         <v>1414</v>
       </c>
+      <c r="AD29" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="54">
         <v>30</v>
       </c>
@@ -9435,8 +9526,11 @@
       <c r="AC30" s="74" t="s">
         <v>1415</v>
       </c>
+      <c r="AD30" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="54">
         <v>31</v>
       </c>
@@ -9532,8 +9626,11 @@
       <c r="AC31" s="74" t="s">
         <v>1368</v>
       </c>
+      <c r="AD31" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="54">
         <v>32</v>
       </c>
@@ -9629,8 +9726,11 @@
       <c r="AC32" s="74" t="s">
         <v>1369</v>
       </c>
+      <c r="AD32" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="54">
         <v>33</v>
       </c>
@@ -9726,8 +9826,11 @@
       <c r="AC33" s="74" t="s">
         <v>1370</v>
       </c>
+      <c r="AD33" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="54">
         <v>34</v>
       </c>
@@ -9823,8 +9926,11 @@
       <c r="AC34" s="74" t="s">
         <v>1371</v>
       </c>
+      <c r="AD34" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="54">
         <v>35</v>
       </c>
@@ -9920,8 +10026,11 @@
       <c r="AC35" s="75" t="s">
         <v>638</v>
       </c>
+      <c r="AD35" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="54">
         <v>36</v>
       </c>
@@ -10017,8 +10126,11 @@
       <c r="AC36" s="75" t="s">
         <v>638</v>
       </c>
+      <c r="AD36" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="54">
         <v>37</v>
       </c>
@@ -10114,8 +10226,11 @@
       <c r="AC37" s="75" t="s">
         <v>638</v>
       </c>
+      <c r="AD37" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="54">
         <v>38</v>
       </c>
@@ -10211,8 +10326,11 @@
       <c r="AC38" s="75" t="s">
         <v>638</v>
       </c>
+      <c r="AD38" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" s="20" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="54">
         <v>39</v>
       </c>
@@ -10308,35 +10426,38 @@
       <c r="AC39" s="75" t="s">
         <v>638</v>
       </c>
+      <c r="AD39" s="37" t="s">
+        <v>638</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B39">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39:F39">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35:F38">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R34">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="S1:X1 AD1:XFD1 A40:P1048576 A1:P1 S40:Y1048576 AA40:AA1048576 AD17:XFD34 AC40:AC1048576 AD40:XFD1048576" numberStoredAsText="1"/>
+    <ignoredError sqref="S1:X1 AE1:XFD1 A40:P1048576 A1:P1 S40:Y1048576 AA40:AA1048576 AE17:XFD34 AC40:AC1048576 AE40:XFD1048576" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -72691,54 +72812,54 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B610 B616:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B611:B615">
-    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R611:W615">
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:W610 T616:Y1048576">
-    <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:AG615">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
